--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="392">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -835,6 +835,9 @@
     <t>['11', '51', '54']</t>
   </si>
   <si>
+    <t>['34', '45+6', '76']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1548,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP288"/>
+  <dimension ref="A1:BP289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1804,7 +1807,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2216,7 +2219,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2628,7 +2631,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2834,7 +2837,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2915,7 +2918,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ7">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3452,7 +3455,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3864,7 +3867,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4276,7 +4279,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4972,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
         <v>0.77</v>
@@ -5100,7 +5103,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5718,7 +5721,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5924,7 +5927,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6130,7 +6133,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6336,7 +6339,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -7778,7 +7781,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7984,7 +7987,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q32">
         <v>4.33</v>
@@ -8396,7 +8399,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8683,7 +8686,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ35">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR35">
         <v>1.31</v>
@@ -8808,7 +8811,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q36">
         <v>4.5</v>
@@ -9014,7 +9017,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -9220,7 +9223,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -9504,7 +9507,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
         <v>1.82</v>
@@ -10044,7 +10047,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q42">
         <v>2.63</v>
@@ -10456,7 +10459,7 @@
         <v>127</v>
       </c>
       <c r="P44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10662,7 +10665,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -11074,7 +11077,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -11692,7 +11695,7 @@
         <v>130</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -12516,7 +12519,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -12722,7 +12725,7 @@
         <v>134</v>
       </c>
       <c r="P55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13134,7 +13137,7 @@
         <v>136</v>
       </c>
       <c r="P57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13212,7 +13215,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ57">
         <v>0.73</v>
@@ -13958,7 +13961,7 @@
         <v>96</v>
       </c>
       <c r="P61" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14370,7 +14373,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14576,7 +14579,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -15194,7 +15197,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15400,7 +15403,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15606,7 +15609,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q69">
         <v>2.4</v>
@@ -15812,7 +15815,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -16018,7 +16021,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q71">
         <v>4.33</v>
@@ -16224,7 +16227,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q72">
         <v>2.3</v>
@@ -16842,7 +16845,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -17048,7 +17051,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17126,7 +17129,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ76">
         <v>2.17</v>
@@ -17254,7 +17257,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17460,7 +17463,7 @@
         <v>150</v>
       </c>
       <c r="P78" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q78">
         <v>3.15</v>
@@ -18078,7 +18081,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18159,7 +18162,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ81">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR81">
         <v>0.8100000000000001</v>
@@ -18902,7 +18905,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19314,7 +19317,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19726,7 +19729,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19932,7 +19935,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20138,7 +20141,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20550,7 +20553,7 @@
         <v>156</v>
       </c>
       <c r="P93" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q93">
         <v>4.75</v>
@@ -20631,7 +20634,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ93">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR93">
         <v>1.4</v>
@@ -20962,7 +20965,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q95">
         <v>3.2</v>
@@ -21168,7 +21171,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21580,7 +21583,7 @@
         <v>96</v>
       </c>
       <c r="P98" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21786,7 +21789,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q99">
         <v>2.75</v>
@@ -22198,7 +22201,7 @@
         <v>161</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22816,7 +22819,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -23512,7 +23515,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ107">
         <v>1.08</v>
@@ -24670,7 +24673,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q113">
         <v>3</v>
@@ -24876,7 +24879,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q114">
         <v>1.91</v>
@@ -25288,7 +25291,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25494,7 +25497,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25700,7 +25703,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -26602,7 +26605,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ122">
         <v>1.18</v>
@@ -27142,7 +27145,7 @@
         <v>180</v>
       </c>
       <c r="P125" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q125">
         <v>4.5</v>
@@ -27348,7 +27351,7 @@
         <v>181</v>
       </c>
       <c r="P126" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -27554,7 +27557,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q127">
         <v>3.2</v>
@@ -27760,7 +27763,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -28378,7 +28381,7 @@
         <v>185</v>
       </c>
       <c r="P131" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -28790,7 +28793,7 @@
         <v>96</v>
       </c>
       <c r="P133" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q133">
         <v>2.3</v>
@@ -29202,7 +29205,7 @@
         <v>99</v>
       </c>
       <c r="P135" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -30026,7 +30029,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -30313,7 +30316,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ140">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR140">
         <v>1.64</v>
@@ -30438,7 +30441,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31262,7 +31265,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q145">
         <v>3.25</v>
@@ -32370,7 +32373,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ150">
         <v>0.8</v>
@@ -32498,7 +32501,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q151">
         <v>4</v>
@@ -32910,7 +32913,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33322,7 +33325,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33528,7 +33531,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -33609,7 +33612,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ156">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR156">
         <v>1.12</v>
@@ -33940,7 +33943,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34764,7 +34767,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q162">
         <v>4.33</v>
@@ -35588,7 +35591,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -35875,7 +35878,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ167">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR167">
         <v>1.5</v>
@@ -36000,7 +36003,7 @@
         <v>96</v>
       </c>
       <c r="P168" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q168">
         <v>3.25</v>
@@ -36412,7 +36415,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q170">
         <v>3.6</v>
@@ -37854,7 +37857,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -38266,7 +38269,7 @@
         <v>96</v>
       </c>
       <c r="P179" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q179">
         <v>4.33</v>
@@ -38678,7 +38681,7 @@
         <v>215</v>
       </c>
       <c r="P181" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -38884,7 +38887,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39296,7 +39299,7 @@
         <v>144</v>
       </c>
       <c r="P184" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>2.4</v>
@@ -39708,7 +39711,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q186">
         <v>2.6</v>
@@ -40120,7 +40123,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40532,7 +40535,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40738,7 +40741,7 @@
         <v>219</v>
       </c>
       <c r="P191" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q191">
         <v>2.4</v>
@@ -41025,7 +41028,7 @@
         <v>1</v>
       </c>
       <c r="AQ192">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR192">
         <v>1.31</v>
@@ -41150,7 +41153,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41356,7 +41359,7 @@
         <v>96</v>
       </c>
       <c r="P194" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q194">
         <v>3.5</v>
@@ -41768,7 +41771,7 @@
         <v>221</v>
       </c>
       <c r="P196" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q196">
         <v>2.4</v>
@@ -42180,7 +42183,7 @@
         <v>223</v>
       </c>
       <c r="P198" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q198">
         <v>4</v>
@@ -42386,7 +42389,7 @@
         <v>224</v>
       </c>
       <c r="P199" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q199">
         <v>2.2</v>
@@ -42798,7 +42801,7 @@
         <v>137</v>
       </c>
       <c r="P201" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -43700,7 +43703,7 @@
         <v>1.44</v>
       </c>
       <c r="AP205">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ205">
         <v>1.08</v>
@@ -44034,7 +44037,7 @@
         <v>119</v>
       </c>
       <c r="P207" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q207">
         <v>4</v>
@@ -44240,7 +44243,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44446,7 +44449,7 @@
         <v>96</v>
       </c>
       <c r="P209" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q209">
         <v>3.1</v>
@@ -44858,7 +44861,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45476,7 +45479,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -46094,7 +46097,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46506,7 +46509,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46712,7 +46715,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -47124,7 +47127,7 @@
         <v>96</v>
       </c>
       <c r="P222" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q222">
         <v>2.88</v>
@@ -47408,7 +47411,7 @@
         <v>0.7</v>
       </c>
       <c r="AP223">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ223">
         <v>0.79</v>
@@ -47536,7 +47539,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -47948,7 +47951,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48360,7 +48363,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48566,7 +48569,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -48853,7 +48856,7 @@
         <v>2</v>
       </c>
       <c r="AQ230">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR230">
         <v>1.34</v>
@@ -48978,7 +48981,7 @@
         <v>96</v>
       </c>
       <c r="P231" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q231">
         <v>4.5</v>
@@ -49184,7 +49187,7 @@
         <v>241</v>
       </c>
       <c r="P232" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q232">
         <v>2.38</v>
@@ -49802,7 +49805,7 @@
         <v>96</v>
       </c>
       <c r="P235" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q235">
         <v>2.6</v>
@@ -50214,7 +50217,7 @@
         <v>245</v>
       </c>
       <c r="P237" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q237">
         <v>2.38</v>
@@ -50420,7 +50423,7 @@
         <v>246</v>
       </c>
       <c r="P238" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q238">
         <v>3.5</v>
@@ -50832,7 +50835,7 @@
         <v>96</v>
       </c>
       <c r="P240" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q240">
         <v>4</v>
@@ -51038,7 +51041,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51656,7 +51659,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -51862,7 +51865,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52068,7 +52071,7 @@
         <v>96</v>
       </c>
       <c r="P246" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q246">
         <v>2.75</v>
@@ -52146,7 +52149,7 @@
         <v>1.2</v>
       </c>
       <c r="AP246">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ246">
         <v>1.25</v>
@@ -52686,7 +52689,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -52892,7 +52895,7 @@
         <v>96</v>
       </c>
       <c r="P250" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53098,7 +53101,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53304,7 +53307,7 @@
         <v>253</v>
       </c>
       <c r="P252" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q252">
         <v>2.5</v>
@@ -53794,7 +53797,7 @@
         <v>1.18</v>
       </c>
       <c r="AP254">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ254">
         <v>1.17</v>
@@ -54334,7 +54337,7 @@
         <v>258</v>
       </c>
       <c r="P257" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q257">
         <v>2.75</v>
@@ -54540,7 +54543,7 @@
         <v>161</v>
       </c>
       <c r="P258" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q258">
         <v>3.1</v>
@@ -55158,7 +55161,7 @@
         <v>260</v>
       </c>
       <c r="P261" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q261">
         <v>2.5</v>
@@ -55776,7 +55779,7 @@
         <v>262</v>
       </c>
       <c r="P264" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q264">
         <v>2.38</v>
@@ -56394,7 +56397,7 @@
         <v>265</v>
       </c>
       <c r="P267" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q267">
         <v>3.75</v>
@@ -56806,7 +56809,7 @@
         <v>267</v>
       </c>
       <c r="P269" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q269">
         <v>3.75</v>
@@ -57012,7 +57015,7 @@
         <v>268</v>
       </c>
       <c r="P270" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q270">
         <v>3.2</v>
@@ -57218,7 +57221,7 @@
         <v>179</v>
       </c>
       <c r="P271" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57711,7 +57714,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ273">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR273">
         <v>1.35</v>
@@ -57836,7 +57839,7 @@
         <v>96</v>
       </c>
       <c r="P274" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q274">
         <v>2.63</v>
@@ -59072,7 +59075,7 @@
         <v>171</v>
       </c>
       <c r="P280" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q280">
         <v>3.6</v>
@@ -59153,7 +59156,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ280">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR280">
         <v>1.31</v>
@@ -59690,7 +59693,7 @@
         <v>118</v>
       </c>
       <c r="P283" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q283">
         <v>2.6</v>
@@ -60102,7 +60105,7 @@
         <v>96</v>
       </c>
       <c r="P285" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q285">
         <v>5.5</v>
@@ -60877,6 +60880,212 @@
       </c>
       <c r="BP288">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7727040</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45668.39583333334</v>
+      </c>
+      <c r="F289">
+        <v>16</v>
+      </c>
+      <c r="G289" t="s">
+        <v>85</v>
+      </c>
+      <c r="H289" t="s">
+        <v>93</v>
+      </c>
+      <c r="I289">
+        <v>2</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>2</v>
+      </c>
+      <c r="L289">
+        <v>3</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>4</v>
+      </c>
+      <c r="O289" t="s">
+        <v>273</v>
+      </c>
+      <c r="P289" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q289">
+        <v>3.4</v>
+      </c>
+      <c r="R289">
+        <v>2.05</v>
+      </c>
+      <c r="S289">
+        <v>3</v>
+      </c>
+      <c r="T289">
+        <v>1.4</v>
+      </c>
+      <c r="U289">
+        <v>2.7</v>
+      </c>
+      <c r="V289">
+        <v>2.8</v>
+      </c>
+      <c r="W289">
+        <v>1.38</v>
+      </c>
+      <c r="X289">
+        <v>6.6</v>
+      </c>
+      <c r="Y289">
+        <v>1.08</v>
+      </c>
+      <c r="Z289">
+        <v>2.75</v>
+      </c>
+      <c r="AA289">
+        <v>3.3</v>
+      </c>
+      <c r="AB289">
+        <v>2.4</v>
+      </c>
+      <c r="AC289">
+        <v>1.06</v>
+      </c>
+      <c r="AD289">
+        <v>8.5</v>
+      </c>
+      <c r="AE289">
+        <v>1.3</v>
+      </c>
+      <c r="AF289">
+        <v>3.45</v>
+      </c>
+      <c r="AG289">
+        <v>1.9</v>
+      </c>
+      <c r="AH289">
+        <v>1.78</v>
+      </c>
+      <c r="AI289">
+        <v>1.65</v>
+      </c>
+      <c r="AJ289">
+        <v>2.05</v>
+      </c>
+      <c r="AK289">
+        <v>1.55</v>
+      </c>
+      <c r="AL289">
+        <v>1.28</v>
+      </c>
+      <c r="AM289">
+        <v>1.4</v>
+      </c>
+      <c r="AN289">
+        <v>1.64</v>
+      </c>
+      <c r="AO289">
+        <v>1.55</v>
+      </c>
+      <c r="AP289">
+        <v>1.75</v>
+      </c>
+      <c r="AQ289">
+        <v>1.42</v>
+      </c>
+      <c r="AR289">
+        <v>1.47</v>
+      </c>
+      <c r="AS289">
+        <v>1.13</v>
+      </c>
+      <c r="AT289">
+        <v>2.6</v>
+      </c>
+      <c r="AU289">
+        <v>7</v>
+      </c>
+      <c r="AV289">
+        <v>3</v>
+      </c>
+      <c r="AW289">
+        <v>12</v>
+      </c>
+      <c r="AX289">
+        <v>10</v>
+      </c>
+      <c r="AY289">
+        <v>20</v>
+      </c>
+      <c r="AZ289">
+        <v>13</v>
+      </c>
+      <c r="BA289">
+        <v>7</v>
+      </c>
+      <c r="BB289">
+        <v>1</v>
+      </c>
+      <c r="BC289">
+        <v>8</v>
+      </c>
+      <c r="BD289">
+        <v>1.95</v>
+      </c>
+      <c r="BE289">
+        <v>6.75</v>
+      </c>
+      <c r="BF289">
+        <v>2</v>
+      </c>
+      <c r="BG289">
+        <v>1.21</v>
+      </c>
+      <c r="BH289">
+        <v>3.8</v>
+      </c>
+      <c r="BI289">
+        <v>1.38</v>
+      </c>
+      <c r="BJ289">
+        <v>2.7</v>
+      </c>
+      <c r="BK289">
+        <v>1.64</v>
+      </c>
+      <c r="BL289">
+        <v>2.1</v>
+      </c>
+      <c r="BM289">
+        <v>1.98</v>
+      </c>
+      <c r="BN289">
+        <v>1.72</v>
+      </c>
+      <c r="BO289">
+        <v>2.48</v>
+      </c>
+      <c r="BP289">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
@@ -61022,19 +61022,19 @@
         <v>2.6</v>
       </c>
       <c r="AU289">
+        <v>8</v>
+      </c>
+      <c r="AV289">
+        <v>3</v>
+      </c>
+      <c r="AW289">
+        <v>10</v>
+      </c>
+      <c r="AX289">
         <v>7</v>
       </c>
-      <c r="AV289">
-        <v>3</v>
-      </c>
-      <c r="AW289">
-        <v>12</v>
-      </c>
-      <c r="AX289">
-        <v>10</v>
-      </c>
       <c r="AY289">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ289">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="393">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -838,6 +838,9 @@
     <t>['34', '45+6', '76']</t>
   </si>
   <si>
+    <t>['17', '48']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1551,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP289"/>
+  <dimension ref="A1:BP290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1807,7 +1810,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2219,7 +2222,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2631,7 +2634,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2837,7 +2840,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -3455,7 +3458,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3867,7 +3870,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4279,7 +4282,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4357,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ14">
         <v>0.73</v>
@@ -5103,7 +5106,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5721,7 +5724,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5927,7 +5930,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6133,7 +6136,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6339,7 +6342,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6626,7 +6629,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -7781,7 +7784,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7987,7 +7990,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q32">
         <v>4.33</v>
@@ -8399,7 +8402,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8811,7 +8814,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q36">
         <v>4.5</v>
@@ -9017,7 +9020,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -9223,7 +9226,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -10047,7 +10050,7 @@
         <v>96</v>
       </c>
       <c r="P42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q42">
         <v>2.63</v>
@@ -10128,7 +10131,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ42">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR42">
         <v>0.79</v>
@@ -10331,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ43">
         <v>1.45</v>
@@ -10459,7 +10462,7 @@
         <v>127</v>
       </c>
       <c r="P44" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10665,7 +10668,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -11077,7 +11080,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -11695,7 +11698,7 @@
         <v>130</v>
       </c>
       <c r="P50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -12519,7 +12522,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -12725,7 +12728,7 @@
         <v>134</v>
       </c>
       <c r="P55" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -13137,7 +13140,7 @@
         <v>136</v>
       </c>
       <c r="P57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13421,7 +13424,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ58">
         <v>1.27</v>
@@ -13961,7 +13964,7 @@
         <v>96</v>
       </c>
       <c r="P61" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q61">
         <v>2.75</v>
@@ -14373,7 +14376,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14579,7 +14582,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14660,7 +14663,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ64">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR64">
         <v>1.77</v>
@@ -15197,7 +15200,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15403,7 +15406,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15609,7 +15612,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q69">
         <v>2.4</v>
@@ -15815,7 +15818,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q70">
         <v>3.1</v>
@@ -16021,7 +16024,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q71">
         <v>4.33</v>
@@ -16227,7 +16230,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q72">
         <v>2.3</v>
@@ -16845,7 +16848,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -17051,7 +17054,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17257,7 +17260,7 @@
         <v>96</v>
       </c>
       <c r="P77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q77">
         <v>2.4</v>
@@ -17463,7 +17466,7 @@
         <v>150</v>
       </c>
       <c r="P78" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q78">
         <v>3.15</v>
@@ -18081,7 +18084,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18365,7 +18368,7 @@
         <v>0.33</v>
       </c>
       <c r="AP82">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ82">
         <v>0.83</v>
@@ -18905,7 +18908,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19192,7 +19195,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ86">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19317,7 +19320,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19729,7 +19732,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19935,7 +19938,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20141,7 +20144,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20553,7 +20556,7 @@
         <v>156</v>
       </c>
       <c r="P93" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q93">
         <v>4.75</v>
@@ -20965,7 +20968,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q95">
         <v>3.2</v>
@@ -21171,7 +21174,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q96">
         <v>3.6</v>
@@ -21583,7 +21586,7 @@
         <v>96</v>
       </c>
       <c r="P98" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q98">
         <v>4.5</v>
@@ -21661,7 +21664,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ98">
         <v>1.17</v>
@@ -21789,7 +21792,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q99">
         <v>2.75</v>
@@ -22201,7 +22204,7 @@
         <v>161</v>
       </c>
       <c r="P101" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>2.5</v>
@@ -22488,7 +22491,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ102">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.15</v>
@@ -22819,7 +22822,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -24673,7 +24676,7 @@
         <v>172</v>
       </c>
       <c r="P113" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q113">
         <v>3</v>
@@ -24879,7 +24882,7 @@
         <v>173</v>
       </c>
       <c r="P114" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q114">
         <v>1.91</v>
@@ -25291,7 +25294,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25497,7 +25500,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25703,7 +25706,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25781,7 +25784,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ118">
         <v>1.18</v>
@@ -26608,7 +26611,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ122">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR122">
         <v>1.58</v>
@@ -27145,7 +27148,7 @@
         <v>180</v>
       </c>
       <c r="P125" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q125">
         <v>4.5</v>
@@ -27351,7 +27354,7 @@
         <v>181</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -27557,7 +27560,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q127">
         <v>3.2</v>
@@ -27763,7 +27766,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -28381,7 +28384,7 @@
         <v>185</v>
       </c>
       <c r="P131" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -28793,7 +28796,7 @@
         <v>96</v>
       </c>
       <c r="P133" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q133">
         <v>2.3</v>
@@ -29205,7 +29208,7 @@
         <v>99</v>
       </c>
       <c r="P135" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -30029,7 +30032,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q139">
         <v>3</v>
@@ -30441,7 +30444,7 @@
         <v>190</v>
       </c>
       <c r="P141" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -31265,7 +31268,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q145">
         <v>3.25</v>
@@ -31346,7 +31349,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ145">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR145">
         <v>1.28</v>
@@ -32501,7 +32504,7 @@
         <v>96</v>
       </c>
       <c r="P151" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q151">
         <v>4</v>
@@ -32579,7 +32582,7 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ151">
         <v>2.08</v>
@@ -32913,7 +32916,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33325,7 +33328,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33531,7 +33534,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -33943,7 +33946,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34767,7 +34770,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q162">
         <v>4.33</v>
@@ -35591,7 +35594,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q166">
         <v>2.75</v>
@@ -36003,7 +36006,7 @@
         <v>96</v>
       </c>
       <c r="P168" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q168">
         <v>3.25</v>
@@ -36415,7 +36418,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q170">
         <v>3.6</v>
@@ -37526,7 +37529,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ175">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37857,7 +37860,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -37935,7 +37938,7 @@
         <v>2.17</v>
       </c>
       <c r="AP177">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ177">
         <v>2.17</v>
@@ -38269,7 +38272,7 @@
         <v>96</v>
       </c>
       <c r="P179" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q179">
         <v>4.33</v>
@@ -38681,7 +38684,7 @@
         <v>215</v>
       </c>
       <c r="P181" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -38887,7 +38890,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39299,7 +39302,7 @@
         <v>144</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q184">
         <v>2.4</v>
@@ -39711,7 +39714,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q186">
         <v>2.6</v>
@@ -40123,7 +40126,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -40535,7 +40538,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40741,7 +40744,7 @@
         <v>219</v>
       </c>
       <c r="P191" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q191">
         <v>2.4</v>
@@ -41153,7 +41156,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41359,7 +41362,7 @@
         <v>96</v>
       </c>
       <c r="P194" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q194">
         <v>3.5</v>
@@ -41771,7 +41774,7 @@
         <v>221</v>
       </c>
       <c r="P196" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q196">
         <v>2.4</v>
@@ -42183,7 +42186,7 @@
         <v>223</v>
       </c>
       <c r="P198" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q198">
         <v>4</v>
@@ -42389,7 +42392,7 @@
         <v>224</v>
       </c>
       <c r="P199" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q199">
         <v>2.2</v>
@@ -42801,7 +42804,7 @@
         <v>137</v>
       </c>
       <c r="P201" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q201">
         <v>2.25</v>
@@ -44037,7 +44040,7 @@
         <v>119</v>
       </c>
       <c r="P207" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q207">
         <v>4</v>
@@ -44115,7 +44118,7 @@
         <v>1.11</v>
       </c>
       <c r="AP207">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ207">
         <v>1.29</v>
@@ -44243,7 +44246,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44449,7 +44452,7 @@
         <v>96</v>
       </c>
       <c r="P209" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q209">
         <v>3.1</v>
@@ -44861,7 +44864,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45148,7 +45151,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ212">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR212">
         <v>1.02</v>
@@ -45479,7 +45482,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -46097,7 +46100,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46509,7 +46512,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46715,7 +46718,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -47127,7 +47130,7 @@
         <v>96</v>
       </c>
       <c r="P222" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q222">
         <v>2.88</v>
@@ -47539,7 +47542,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -47617,7 +47620,7 @@
         <v>2.1</v>
       </c>
       <c r="AP224">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ224">
         <v>2.08</v>
@@ -47951,7 +47954,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48363,7 +48366,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48569,7 +48572,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -48981,7 +48984,7 @@
         <v>96</v>
       </c>
       <c r="P231" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q231">
         <v>4.5</v>
@@ -49187,7 +49190,7 @@
         <v>241</v>
       </c>
       <c r="P232" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q232">
         <v>2.38</v>
@@ -49680,7 +49683,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ234">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR234">
         <v>1.1</v>
@@ -49805,7 +49808,7 @@
         <v>96</v>
       </c>
       <c r="P235" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q235">
         <v>2.6</v>
@@ -50217,7 +50220,7 @@
         <v>245</v>
       </c>
       <c r="P237" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q237">
         <v>2.38</v>
@@ -50423,7 +50426,7 @@
         <v>246</v>
       </c>
       <c r="P238" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q238">
         <v>3.5</v>
@@ -50835,7 +50838,7 @@
         <v>96</v>
       </c>
       <c r="P240" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q240">
         <v>4</v>
@@ -51041,7 +51044,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51659,7 +51662,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -51865,7 +51868,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52071,7 +52074,7 @@
         <v>96</v>
       </c>
       <c r="P246" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q246">
         <v>2.75</v>
@@ -52689,7 +52692,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -52895,7 +52898,7 @@
         <v>96</v>
       </c>
       <c r="P250" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53101,7 +53104,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53307,7 +53310,7 @@
         <v>253</v>
       </c>
       <c r="P252" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q252">
         <v>2.5</v>
@@ -53591,7 +53594,7 @@
         <v>1.27</v>
       </c>
       <c r="AP253">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ253">
         <v>1.08</v>
@@ -54209,7 +54212,7 @@
         <v>0.58</v>
       </c>
       <c r="AP256">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AQ256">
         <v>0.79</v>
@@ -54337,7 +54340,7 @@
         <v>258</v>
       </c>
       <c r="P257" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q257">
         <v>2.75</v>
@@ -54543,7 +54546,7 @@
         <v>161</v>
       </c>
       <c r="P258" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q258">
         <v>3.1</v>
@@ -55161,7 +55164,7 @@
         <v>260</v>
       </c>
       <c r="P261" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q261">
         <v>2.5</v>
@@ -55779,7 +55782,7 @@
         <v>262</v>
       </c>
       <c r="P264" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q264">
         <v>2.38</v>
@@ -56397,7 +56400,7 @@
         <v>265</v>
       </c>
       <c r="P267" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q267">
         <v>3.75</v>
@@ -56809,7 +56812,7 @@
         <v>267</v>
       </c>
       <c r="P269" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q269">
         <v>3.75</v>
@@ -57015,7 +57018,7 @@
         <v>268</v>
       </c>
       <c r="P270" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q270">
         <v>3.2</v>
@@ -57221,7 +57224,7 @@
         <v>179</v>
       </c>
       <c r="P271" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57839,7 +57842,7 @@
         <v>96</v>
       </c>
       <c r="P274" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q274">
         <v>2.63</v>
@@ -58126,7 +58129,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ275">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR275">
         <v>1.64</v>
@@ -59075,7 +59078,7 @@
         <v>171</v>
       </c>
       <c r="P280" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q280">
         <v>3.6</v>
@@ -59693,7 +59696,7 @@
         <v>118</v>
       </c>
       <c r="P283" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q283">
         <v>2.6</v>
@@ -60105,7 +60108,7 @@
         <v>96</v>
       </c>
       <c r="P285" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q285">
         <v>5.5</v>
@@ -61086,6 +61089,212 @@
       </c>
       <c r="BP289">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7727172</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45673.70833333334</v>
+      </c>
+      <c r="F290">
+        <v>27</v>
+      </c>
+      <c r="G290" t="s">
+        <v>82</v>
+      </c>
+      <c r="H290" t="s">
+        <v>71</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290">
+        <v>2</v>
+      </c>
+      <c r="L290">
+        <v>2</v>
+      </c>
+      <c r="M290">
+        <v>1</v>
+      </c>
+      <c r="N290">
+        <v>3</v>
+      </c>
+      <c r="O290" t="s">
+        <v>274</v>
+      </c>
+      <c r="P290" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q290">
+        <v>4.33</v>
+      </c>
+      <c r="R290">
+        <v>2.05</v>
+      </c>
+      <c r="S290">
+        <v>2.5</v>
+      </c>
+      <c r="T290">
+        <v>1.42</v>
+      </c>
+      <c r="U290">
+        <v>2.62</v>
+      </c>
+      <c r="V290">
+        <v>3</v>
+      </c>
+      <c r="W290">
+        <v>1.33</v>
+      </c>
+      <c r="X290">
+        <v>6.9</v>
+      </c>
+      <c r="Y290">
+        <v>1.07</v>
+      </c>
+      <c r="Z290">
+        <v>4.33</v>
+      </c>
+      <c r="AA290">
+        <v>3.4</v>
+      </c>
+      <c r="AB290">
+        <v>1.87</v>
+      </c>
+      <c r="AC290">
+        <v>1.06</v>
+      </c>
+      <c r="AD290">
+        <v>8.5</v>
+      </c>
+      <c r="AE290">
+        <v>1.35</v>
+      </c>
+      <c r="AF290">
+        <v>3.1</v>
+      </c>
+      <c r="AG290">
+        <v>2.2</v>
+      </c>
+      <c r="AH290">
+        <v>1.65</v>
+      </c>
+      <c r="AI290">
+        <v>1.85</v>
+      </c>
+      <c r="AJ290">
+        <v>1.8</v>
+      </c>
+      <c r="AK290">
+        <v>1.91</v>
+      </c>
+      <c r="AL290">
+        <v>1.25</v>
+      </c>
+      <c r="AM290">
+        <v>1.22</v>
+      </c>
+      <c r="AN290">
+        <v>0.92</v>
+      </c>
+      <c r="AO290">
+        <v>1.18</v>
+      </c>
+      <c r="AP290">
+        <v>1.08</v>
+      </c>
+      <c r="AQ290">
+        <v>1.08</v>
+      </c>
+      <c r="AR290">
+        <v>1.02</v>
+      </c>
+      <c r="AS290">
+        <v>1.2</v>
+      </c>
+      <c r="AT290">
+        <v>2.22</v>
+      </c>
+      <c r="AU290">
+        <v>3</v>
+      </c>
+      <c r="AV290">
+        <v>3</v>
+      </c>
+      <c r="AW290">
+        <v>5</v>
+      </c>
+      <c r="AX290">
+        <v>10</v>
+      </c>
+      <c r="AY290">
+        <v>8</v>
+      </c>
+      <c r="AZ290">
+        <v>16</v>
+      </c>
+      <c r="BA290">
+        <v>2</v>
+      </c>
+      <c r="BB290">
+        <v>4</v>
+      </c>
+      <c r="BC290">
+        <v>6</v>
+      </c>
+      <c r="BD290">
+        <v>2.48</v>
+      </c>
+      <c r="BE290">
+        <v>6.75</v>
+      </c>
+      <c r="BF290">
+        <v>1.65</v>
+      </c>
+      <c r="BG290">
+        <v>1.28</v>
+      </c>
+      <c r="BH290">
+        <v>3.2</v>
+      </c>
+      <c r="BI290">
+        <v>1.49</v>
+      </c>
+      <c r="BJ290">
+        <v>2.4</v>
+      </c>
+      <c r="BK290">
+        <v>1.79</v>
+      </c>
+      <c r="BL290">
+        <v>1.9</v>
+      </c>
+      <c r="BM290">
+        <v>2.23</v>
+      </c>
+      <c r="BN290">
+        <v>1.56</v>
+      </c>
+      <c r="BO290">
+        <v>2.88</v>
+      </c>
+      <c r="BP290">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="409">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -859,6 +859,12 @@
     <t>['45+2']</t>
   </si>
   <si>
+    <t>['55']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1105,9 +1111,6 @@
     <t>['33', '80']</t>
   </si>
   <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['27', '54']</t>
   </si>
   <si>
@@ -1232,6 +1235,12 @@
   </si>
   <si>
     <t>['5', '13', '68']</t>
+  </si>
+  <si>
+    <t>['71', '86']</t>
+  </si>
+  <si>
+    <t>['34', '59']</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP301"/>
+  <dimension ref="A1:BP304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1849,7 +1858,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2261,7 +2270,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2339,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2673,7 +2682,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2751,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -2879,7 +2888,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -3497,7 +3506,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3909,7 +3918,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4321,7 +4330,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -5145,7 +5154,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5763,7 +5772,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5969,7 +5978,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6175,7 +6184,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6381,7 +6390,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6462,7 +6471,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6665,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>1.08</v>
@@ -7695,7 +7704,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
         <v>0.6899999999999999</v>
@@ -7823,7 +7832,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8029,7 +8038,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8441,7 +8450,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8853,7 +8862,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9059,7 +9068,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q37">
         <v>4.33</v>
@@ -9265,7 +9274,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -10170,7 +10179,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR42">
         <v>1.98</v>
@@ -10295,7 +10304,7 @@
         <v>96</v>
       </c>
       <c r="P43" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10373,7 +10382,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
         <v>1.08</v>
@@ -10582,7 +10591,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
         <v>1.4</v>
@@ -10707,7 +10716,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -11119,7 +11128,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -11197,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>1.08</v>
@@ -11531,7 +11540,7 @@
         <v>129</v>
       </c>
       <c r="P49" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q49">
         <v>3</v>
@@ -11737,7 +11746,7 @@
         <v>130</v>
       </c>
       <c r="P50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -12561,7 +12570,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -13054,7 +13063,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ56">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR56">
         <v>1.21</v>
@@ -13179,7 +13188,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13260,7 +13269,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ57">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>1.85</v>
@@ -13385,7 +13394,7 @@
         <v>136</v>
       </c>
       <c r="P58" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q58">
         <v>2.75</v>
@@ -13463,7 +13472,7 @@
         <v>3</v>
       </c>
       <c r="AP58">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ58">
         <v>1.21</v>
@@ -13797,7 +13806,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14415,7 +14424,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14493,7 +14502,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>1.75</v>
@@ -14621,7 +14630,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -15239,7 +15248,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15445,7 +15454,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15651,7 +15660,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15857,7 +15866,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q70">
         <v>4.33</v>
@@ -16063,7 +16072,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -16269,7 +16278,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q72">
         <v>2.05</v>
@@ -16347,7 +16356,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ72">
         <v>0.77</v>
@@ -16887,7 +16896,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -16965,7 +16974,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75">
         <v>1.08</v>
@@ -17093,7 +17102,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17377,7 +17386,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>0.8</v>
@@ -17505,7 +17514,7 @@
         <v>96</v>
       </c>
       <c r="P78" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q78">
         <v>2.4</v>
@@ -17711,7 +17720,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q79">
         <v>3.15</v>
@@ -18123,7 +18132,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18616,7 +18625,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ83">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR83">
         <v>1.2</v>
@@ -18819,7 +18828,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ84">
         <v>1.08</v>
@@ -18947,7 +18956,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19359,7 +19368,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19646,7 +19655,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ88">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR88">
         <v>1.55</v>
@@ -19771,7 +19780,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19977,7 +19986,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20183,7 +20192,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20389,7 +20398,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20673,7 +20682,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
         <v>0.73</v>
@@ -21007,7 +21016,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q95">
         <v>4.5</v>
@@ -21419,7 +21428,7 @@
         <v>96</v>
       </c>
       <c r="P97" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21831,7 +21840,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q99">
         <v>3.6</v>
@@ -21912,7 +21921,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR99">
         <v>1.12</v>
@@ -22037,7 +22046,7 @@
         <v>160</v>
       </c>
       <c r="P100" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q100">
         <v>2.5</v>
@@ -22449,7 +22458,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q102">
         <v>2.75</v>
@@ -22736,7 +22745,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ103">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -22861,7 +22870,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -22939,7 +22948,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>0.8</v>
@@ -24303,7 +24312,7 @@
         <v>170</v>
       </c>
       <c r="P111" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -24509,7 +24518,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q112">
         <v>1.91</v>
@@ -24587,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="AP112">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ112">
         <v>0.5</v>
@@ -25333,7 +25342,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25411,7 +25420,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ116">
         <v>0.83</v>
@@ -25539,7 +25548,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25745,7 +25754,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -26569,7 +26578,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q122">
         <v>4.5</v>
@@ -26775,7 +26784,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q123">
         <v>2</v>
@@ -26981,7 +26990,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q124">
         <v>3.2</v>
@@ -27677,10 +27686,10 @@
         <v>0.6</v>
       </c>
       <c r="AP127">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ127">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR127">
         <v>1.5</v>
@@ -27805,7 +27814,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -28423,7 +28432,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -29119,7 +29128,7 @@
         <v>1.4</v>
       </c>
       <c r="AP134">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ134">
         <v>1.29</v>
@@ -29247,7 +29256,7 @@
         <v>96</v>
       </c>
       <c r="P135" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29453,7 +29462,7 @@
         <v>188</v>
       </c>
       <c r="P136" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q136">
         <v>2.88</v>
@@ -29534,7 +29543,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ136">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR136">
         <v>1.54</v>
@@ -29865,7 +29874,7 @@
         <v>189</v>
       </c>
       <c r="P138" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q138">
         <v>3</v>
@@ -29943,7 +29952,7 @@
         <v>2.25</v>
       </c>
       <c r="AP138">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ138">
         <v>1.58</v>
@@ -30277,7 +30286,7 @@
         <v>99</v>
       </c>
       <c r="P140" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -31101,7 +31110,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q144">
         <v>3.25</v>
@@ -32131,7 +32140,7 @@
         <v>96</v>
       </c>
       <c r="P149" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32624,7 +32633,7 @@
         <v>1</v>
       </c>
       <c r="AQ151">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR151">
         <v>1.31</v>
@@ -32827,7 +32836,7 @@
         <v>1.17</v>
       </c>
       <c r="AP152">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ152">
         <v>0.73</v>
@@ -32955,7 +32964,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33367,7 +33376,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33573,7 +33582,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -33985,7 +33994,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34809,7 +34818,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q162">
         <v>3.6</v>
@@ -35221,7 +35230,7 @@
         <v>96</v>
       </c>
       <c r="P164" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q164">
         <v>3.25</v>
@@ -35299,7 +35308,7 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
         <v>2.14</v>
@@ -35427,7 +35436,7 @@
         <v>206</v>
       </c>
       <c r="P165" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35711,7 +35720,7 @@
         <v>0.5</v>
       </c>
       <c r="AP166">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ166">
         <v>0.46</v>
@@ -36126,7 +36135,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ168">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR168">
         <v>1.49</v>
@@ -36457,7 +36466,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q170">
         <v>4.33</v>
@@ -37771,7 +37780,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1.29</v>
@@ -37899,7 +37908,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -38598,7 +38607,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ180">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR180">
         <v>1.41</v>
@@ -38723,7 +38732,7 @@
         <v>216</v>
       </c>
       <c r="P181" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -38929,7 +38938,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39547,7 +39556,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39753,7 +39762,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q186">
         <v>4.33</v>
@@ -39959,7 +39968,7 @@
         <v>143</v>
       </c>
       <c r="P187" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40037,7 +40046,7 @@
         <v>0.71</v>
       </c>
       <c r="AP187">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ187">
         <v>1.08</v>
@@ -40165,7 +40174,7 @@
         <v>218</v>
       </c>
       <c r="P188" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40243,7 +40252,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ188">
         <v>0.79</v>
@@ -40577,7 +40586,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q190">
         <v>3.75</v>
@@ -40783,7 +40792,7 @@
         <v>96</v>
       </c>
       <c r="P191" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q191">
         <v>3.5</v>
@@ -41195,7 +41204,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41607,7 +41616,7 @@
         <v>221</v>
       </c>
       <c r="P195" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q195">
         <v>2.4</v>
@@ -41813,7 +41822,7 @@
         <v>96</v>
       </c>
       <c r="P196" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q196">
         <v>3.6</v>
@@ -41894,7 +41903,7 @@
         <v>0.46</v>
       </c>
       <c r="AQ196">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR196">
         <v>1.04</v>
@@ -42225,7 +42234,7 @@
         <v>137</v>
       </c>
       <c r="P198" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q198">
         <v>2.25</v>
@@ -42431,7 +42440,7 @@
         <v>223</v>
       </c>
       <c r="P199" t="s">
-        <v>363</v>
+        <v>282</v>
       </c>
       <c r="Q199">
         <v>2.2</v>
@@ -42509,7 +42518,7 @@
         <v>1.71</v>
       </c>
       <c r="AP199">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ199">
         <v>1.58</v>
@@ -42843,7 +42852,7 @@
         <v>224</v>
       </c>
       <c r="P201" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q201">
         <v>4</v>
@@ -43873,7 +43882,7 @@
         <v>119</v>
       </c>
       <c r="P206" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q206">
         <v>4</v>
@@ -44285,7 +44294,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44363,10 +44372,10 @@
         <v>0.43</v>
       </c>
       <c r="AP208">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ208">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR208">
         <v>1.3</v>
@@ -44572,7 +44581,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ209">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR209">
         <v>1.37</v>
@@ -44697,7 +44706,7 @@
         <v>96</v>
       </c>
       <c r="P210" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44775,7 +44784,7 @@
         <v>0.88</v>
       </c>
       <c r="AP210">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ210">
         <v>1.42</v>
@@ -44903,7 +44912,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45521,7 +45530,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -46139,7 +46148,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46426,7 +46435,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ218">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR218">
         <v>1.48</v>
@@ -46551,7 +46560,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46629,7 +46638,7 @@
         <v>1</v>
       </c>
       <c r="AP219">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ219">
         <v>1.38</v>
@@ -46757,7 +46766,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -46835,7 +46844,7 @@
         <v>0.89</v>
       </c>
       <c r="AP220">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ220">
         <v>0.6899999999999999</v>
@@ -47169,7 +47178,7 @@
         <v>96</v>
       </c>
       <c r="P222" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q222">
         <v>2.88</v>
@@ -47581,7 +47590,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -47993,7 +48002,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48405,7 +48414,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48611,7 +48620,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -49023,7 +49032,7 @@
         <v>241</v>
       </c>
       <c r="P231" t="s">
-        <v>363</v>
+        <v>282</v>
       </c>
       <c r="Q231">
         <v>2.38</v>
@@ -49229,7 +49238,7 @@
         <v>96</v>
       </c>
       <c r="P232" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q232">
         <v>4.5</v>
@@ -49847,7 +49856,7 @@
         <v>244</v>
       </c>
       <c r="P235" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -50259,7 +50268,7 @@
         <v>96</v>
       </c>
       <c r="P237" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q237">
         <v>2.6</v>
@@ -50465,7 +50474,7 @@
         <v>245</v>
       </c>
       <c r="P238" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q238">
         <v>2.38</v>
@@ -50543,7 +50552,7 @@
         <v>0.44</v>
       </c>
       <c r="AP238">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ238">
         <v>0.5</v>
@@ -50671,7 +50680,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q239">
         <v>4</v>
@@ -50752,7 +50761,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ239">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR239">
         <v>1.24</v>
@@ -51083,7 +51092,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51576,7 +51585,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ243">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR243">
         <v>1.71</v>
@@ -51701,7 +51710,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -51779,7 +51788,7 @@
         <v>1.9</v>
       </c>
       <c r="AP244">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ244">
         <v>1.92</v>
@@ -51907,7 +51916,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52525,7 +52534,7 @@
         <v>96</v>
       </c>
       <c r="P248" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q248">
         <v>2.75</v>
@@ -52603,7 +52612,7 @@
         <v>1.44</v>
       </c>
       <c r="AP248">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ248">
         <v>1.58</v>
@@ -52731,7 +52740,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -52937,7 +52946,7 @@
         <v>253</v>
       </c>
       <c r="P250" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53143,7 +53152,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53349,7 +53358,7 @@
         <v>96</v>
       </c>
       <c r="P252" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q252">
         <v>2.75</v>
@@ -54173,7 +54182,7 @@
         <v>257</v>
       </c>
       <c r="P256" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q256">
         <v>2.75</v>
@@ -54379,7 +54388,7 @@
         <v>160</v>
       </c>
       <c r="P257" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q257">
         <v>3.1</v>
@@ -54457,7 +54466,7 @@
         <v>2</v>
       </c>
       <c r="AP257">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ257">
         <v>1.92</v>
@@ -54872,7 +54881,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ259">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR259">
         <v>1.32</v>
@@ -54997,7 +55006,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q260">
         <v>2.5</v>
@@ -55281,7 +55290,7 @@
         <v>1.17</v>
       </c>
       <c r="AP261">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ261">
         <v>1.21</v>
@@ -55821,7 +55830,7 @@
         <v>262</v>
       </c>
       <c r="P264" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q264">
         <v>2.38</v>
@@ -56439,7 +56448,7 @@
         <v>265</v>
       </c>
       <c r="P267" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q267">
         <v>3.75</v>
@@ -57263,7 +57272,7 @@
         <v>268</v>
       </c>
       <c r="P271" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q271">
         <v>3.75</v>
@@ -57469,7 +57478,7 @@
         <v>269</v>
       </c>
       <c r="P272" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q272">
         <v>3.2</v>
@@ -57675,7 +57684,7 @@
         <v>96</v>
       </c>
       <c r="P273" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q273">
         <v>2.63</v>
@@ -57881,7 +57890,7 @@
         <v>183</v>
       </c>
       <c r="P274" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q274">
         <v>3.25</v>
@@ -59117,7 +59126,7 @@
         <v>96</v>
       </c>
       <c r="P280" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q280">
         <v>5.5</v>
@@ -59195,7 +59204,7 @@
         <v>2.09</v>
       </c>
       <c r="AP280">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ280">
         <v>2.17</v>
@@ -59323,7 +59332,7 @@
         <v>118</v>
       </c>
       <c r="P281" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q281">
         <v>2.6</v>
@@ -59941,7 +59950,7 @@
         <v>172</v>
       </c>
       <c r="P284" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -61461,7 +61470,7 @@
         <v>1.45</v>
       </c>
       <c r="AP291">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ291">
         <v>1.42</v>
@@ -61589,7 +61598,7 @@
         <v>275</v>
       </c>
       <c r="P292" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q292">
         <v>3.4</v>
@@ -62001,7 +62010,7 @@
         <v>276</v>
       </c>
       <c r="P294" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q294">
         <v>2</v>
@@ -62079,7 +62088,7 @@
         <v>0.42</v>
       </c>
       <c r="AP294">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ294">
         <v>0.46</v>
@@ -62207,7 +62216,7 @@
         <v>132</v>
       </c>
       <c r="P295" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q295">
         <v>2.75</v>
@@ -62288,7 +62297,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ295">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR295">
         <v>0.91</v>
@@ -62413,7 +62422,7 @@
         <v>137</v>
       </c>
       <c r="P296" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q296">
         <v>3.25</v>
@@ -62619,7 +62628,7 @@
         <v>277</v>
       </c>
       <c r="P297" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q297">
         <v>3.2</v>
@@ -62825,7 +62834,7 @@
         <v>278</v>
       </c>
       <c r="P298" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q298">
         <v>3.25</v>
@@ -62906,7 +62915,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ298">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR298">
         <v>1.53</v>
@@ -63031,7 +63040,7 @@
         <v>264</v>
       </c>
       <c r="P299" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q299">
         <v>3.6</v>
@@ -63600,6 +63609,624 @@
       </c>
       <c r="BP301">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7727152</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F302">
+        <v>26</v>
+      </c>
+      <c r="G302" t="s">
+        <v>93</v>
+      </c>
+      <c r="H302" t="s">
+        <v>83</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>1</v>
+      </c>
+      <c r="M302">
+        <v>2</v>
+      </c>
+      <c r="N302">
+        <v>3</v>
+      </c>
+      <c r="O302" t="s">
+        <v>281</v>
+      </c>
+      <c r="P302" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q302">
+        <v>2.88</v>
+      </c>
+      <c r="R302">
+        <v>2.2</v>
+      </c>
+      <c r="S302">
+        <v>3.75</v>
+      </c>
+      <c r="T302">
+        <v>1.4</v>
+      </c>
+      <c r="U302">
+        <v>2.75</v>
+      </c>
+      <c r="V302">
+        <v>2.75</v>
+      </c>
+      <c r="W302">
+        <v>1.4</v>
+      </c>
+      <c r="X302">
+        <v>8</v>
+      </c>
+      <c r="Y302">
+        <v>1.08</v>
+      </c>
+      <c r="Z302">
+        <v>2.1</v>
+      </c>
+      <c r="AA302">
+        <v>3.4</v>
+      </c>
+      <c r="AB302">
+        <v>3.4</v>
+      </c>
+      <c r="AC302">
+        <v>1.06</v>
+      </c>
+      <c r="AD302">
+        <v>8.5</v>
+      </c>
+      <c r="AE302">
+        <v>1.3</v>
+      </c>
+      <c r="AF302">
+        <v>3.35</v>
+      </c>
+      <c r="AG302">
+        <v>1.91</v>
+      </c>
+      <c r="AH302">
+        <v>1.83</v>
+      </c>
+      <c r="AI302">
+        <v>1.75</v>
+      </c>
+      <c r="AJ302">
+        <v>2</v>
+      </c>
+      <c r="AK302">
+        <v>1.3</v>
+      </c>
+      <c r="AL302">
+        <v>1.25</v>
+      </c>
+      <c r="AM302">
+        <v>1.67</v>
+      </c>
+      <c r="AN302">
+        <v>1.62</v>
+      </c>
+      <c r="AO302">
+        <v>1.17</v>
+      </c>
+      <c r="AP302">
+        <v>1.5</v>
+      </c>
+      <c r="AQ302">
+        <v>1.31</v>
+      </c>
+      <c r="AR302">
+        <v>1.68</v>
+      </c>
+      <c r="AS302">
+        <v>1.27</v>
+      </c>
+      <c r="AT302">
+        <v>2.95</v>
+      </c>
+      <c r="AU302">
+        <v>8</v>
+      </c>
+      <c r="AV302">
+        <v>4</v>
+      </c>
+      <c r="AW302">
+        <v>11</v>
+      </c>
+      <c r="AX302">
+        <v>9</v>
+      </c>
+      <c r="AY302">
+        <v>20</v>
+      </c>
+      <c r="AZ302">
+        <v>13</v>
+      </c>
+      <c r="BA302">
+        <v>5</v>
+      </c>
+      <c r="BB302">
+        <v>5</v>
+      </c>
+      <c r="BC302">
+        <v>10</v>
+      </c>
+      <c r="BD302">
+        <v>1.62</v>
+      </c>
+      <c r="BE302">
+        <v>7.2</v>
+      </c>
+      <c r="BF302">
+        <v>2.99</v>
+      </c>
+      <c r="BG302">
+        <v>1.25</v>
+      </c>
+      <c r="BH302">
+        <v>3.6</v>
+      </c>
+      <c r="BI302">
+        <v>1.25</v>
+      </c>
+      <c r="BJ302">
+        <v>3.28</v>
+      </c>
+      <c r="BK302">
+        <v>1.48</v>
+      </c>
+      <c r="BL302">
+        <v>2.4</v>
+      </c>
+      <c r="BM302">
+        <v>1.85</v>
+      </c>
+      <c r="BN302">
+        <v>1.85</v>
+      </c>
+      <c r="BO302">
+        <v>2.3</v>
+      </c>
+      <c r="BP302">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7727157</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F303">
+        <v>26</v>
+      </c>
+      <c r="G303" t="s">
+        <v>74</v>
+      </c>
+      <c r="H303" t="s">
+        <v>81</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>1</v>
+      </c>
+      <c r="L303">
+        <v>1</v>
+      </c>
+      <c r="M303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>2</v>
+      </c>
+      <c r="O303" t="s">
+        <v>282</v>
+      </c>
+      <c r="P303" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q303">
+        <v>2.63</v>
+      </c>
+      <c r="R303">
+        <v>2.3</v>
+      </c>
+      <c r="S303">
+        <v>3.6</v>
+      </c>
+      <c r="T303">
+        <v>1.3</v>
+      </c>
+      <c r="U303">
+        <v>3.4</v>
+      </c>
+      <c r="V303">
+        <v>2.5</v>
+      </c>
+      <c r="W303">
+        <v>1.5</v>
+      </c>
+      <c r="X303">
+        <v>6</v>
+      </c>
+      <c r="Y303">
+        <v>1.13</v>
+      </c>
+      <c r="Z303">
+        <v>2.1</v>
+      </c>
+      <c r="AA303">
+        <v>3.5</v>
+      </c>
+      <c r="AB303">
+        <v>3.4</v>
+      </c>
+      <c r="AC303">
+        <v>1.02</v>
+      </c>
+      <c r="AD303">
+        <v>17</v>
+      </c>
+      <c r="AE303">
+        <v>1.18</v>
+      </c>
+      <c r="AF303">
+        <v>4.75</v>
+      </c>
+      <c r="AG303">
+        <v>1.65</v>
+      </c>
+      <c r="AH303">
+        <v>2.15</v>
+      </c>
+      <c r="AI303">
+        <v>1.67</v>
+      </c>
+      <c r="AJ303">
+        <v>2.1</v>
+      </c>
+      <c r="AK303">
+        <v>1.32</v>
+      </c>
+      <c r="AL303">
+        <v>1.28</v>
+      </c>
+      <c r="AM303">
+        <v>1.71</v>
+      </c>
+      <c r="AN303">
+        <v>1.29</v>
+      </c>
+      <c r="AO303">
+        <v>1.08</v>
+      </c>
+      <c r="AP303">
+        <v>1.27</v>
+      </c>
+      <c r="AQ303">
+        <v>1.08</v>
+      </c>
+      <c r="AR303">
+        <v>1.22</v>
+      </c>
+      <c r="AS303">
+        <v>0.87</v>
+      </c>
+      <c r="AT303">
+        <v>2.09</v>
+      </c>
+      <c r="AU303">
+        <v>4</v>
+      </c>
+      <c r="AV303">
+        <v>6</v>
+      </c>
+      <c r="AW303">
+        <v>8</v>
+      </c>
+      <c r="AX303">
+        <v>5</v>
+      </c>
+      <c r="AY303">
+        <v>13</v>
+      </c>
+      <c r="AZ303">
+        <v>13</v>
+      </c>
+      <c r="BA303">
+        <v>5</v>
+      </c>
+      <c r="BB303">
+        <v>4</v>
+      </c>
+      <c r="BC303">
+        <v>9</v>
+      </c>
+      <c r="BD303">
+        <v>1.84</v>
+      </c>
+      <c r="BE303">
+        <v>6.8</v>
+      </c>
+      <c r="BF303">
+        <v>2.48</v>
+      </c>
+      <c r="BG303">
+        <v>1.2</v>
+      </c>
+      <c r="BH303">
+        <v>4</v>
+      </c>
+      <c r="BI303">
+        <v>1.25</v>
+      </c>
+      <c r="BJ303">
+        <v>3.28</v>
+      </c>
+      <c r="BK303">
+        <v>1.48</v>
+      </c>
+      <c r="BL303">
+        <v>2.4</v>
+      </c>
+      <c r="BM303">
+        <v>1.85</v>
+      </c>
+      <c r="BN303">
+        <v>1.85</v>
+      </c>
+      <c r="BO303">
+        <v>2.3</v>
+      </c>
+      <c r="BP303">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7727042</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45678.69791666666</v>
+      </c>
+      <c r="F304">
+        <v>16</v>
+      </c>
+      <c r="G304" t="s">
+        <v>72</v>
+      </c>
+      <c r="H304" t="s">
+        <v>78</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <v>1</v>
+      </c>
+      <c r="K304">
+        <v>2</v>
+      </c>
+      <c r="L304">
+        <v>1</v>
+      </c>
+      <c r="M304">
+        <v>2</v>
+      </c>
+      <c r="N304">
+        <v>3</v>
+      </c>
+      <c r="O304" t="s">
+        <v>94</v>
+      </c>
+      <c r="P304" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q304">
+        <v>2.25</v>
+      </c>
+      <c r="R304">
+        <v>2.2</v>
+      </c>
+      <c r="S304">
+        <v>4.5</v>
+      </c>
+      <c r="T304">
+        <v>1.36</v>
+      </c>
+      <c r="U304">
+        <v>2.88</v>
+      </c>
+      <c r="V304">
+        <v>2.65</v>
+      </c>
+      <c r="W304">
+        <v>1.42</v>
+      </c>
+      <c r="X304">
+        <v>6.4</v>
+      </c>
+      <c r="Y304">
+        <v>1.08</v>
+      </c>
+      <c r="Z304">
+        <v>1.7</v>
+      </c>
+      <c r="AA304">
+        <v>3.5</v>
+      </c>
+      <c r="AB304">
+        <v>5.25</v>
+      </c>
+      <c r="AC304">
+        <v>1.05</v>
+      </c>
+      <c r="AD304">
+        <v>9</v>
+      </c>
+      <c r="AE304">
+        <v>1.28</v>
+      </c>
+      <c r="AF304">
+        <v>3.5</v>
+      </c>
+      <c r="AG304">
+        <v>2.2</v>
+      </c>
+      <c r="AH304">
+        <v>1.6</v>
+      </c>
+      <c r="AI304">
+        <v>1.77</v>
+      </c>
+      <c r="AJ304">
+        <v>1.9</v>
+      </c>
+      <c r="AK304">
+        <v>1.18</v>
+      </c>
+      <c r="AL304">
+        <v>1.22</v>
+      </c>
+      <c r="AM304">
+        <v>2.05</v>
+      </c>
+      <c r="AN304">
+        <v>1.09</v>
+      </c>
+      <c r="AO304">
+        <v>0.75</v>
+      </c>
+      <c r="AP304">
+        <v>1</v>
+      </c>
+      <c r="AQ304">
+        <v>0.92</v>
+      </c>
+      <c r="AR304">
+        <v>1.18</v>
+      </c>
+      <c r="AS304">
+        <v>1.06</v>
+      </c>
+      <c r="AT304">
+        <v>2.24</v>
+      </c>
+      <c r="AU304">
+        <v>4</v>
+      </c>
+      <c r="AV304">
+        <v>4</v>
+      </c>
+      <c r="AW304">
+        <v>9</v>
+      </c>
+      <c r="AX304">
+        <v>6</v>
+      </c>
+      <c r="AY304">
+        <v>16</v>
+      </c>
+      <c r="AZ304">
+        <v>12</v>
+      </c>
+      <c r="BA304">
+        <v>3</v>
+      </c>
+      <c r="BB304">
+        <v>3</v>
+      </c>
+      <c r="BC304">
+        <v>6</v>
+      </c>
+      <c r="BD304">
+        <v>1.33</v>
+      </c>
+      <c r="BE304">
+        <v>9.9</v>
+      </c>
+      <c r="BF304">
+        <v>4.15</v>
+      </c>
+      <c r="BG304">
+        <v>1.22</v>
+      </c>
+      <c r="BH304">
+        <v>3.5</v>
+      </c>
+      <c r="BI304">
+        <v>1.44</v>
+      </c>
+      <c r="BJ304">
+        <v>2.51</v>
+      </c>
+      <c r="BK304">
+        <v>1.77</v>
+      </c>
+      <c r="BL304">
+        <v>1.95</v>
+      </c>
+      <c r="BM304">
+        <v>2.27</v>
+      </c>
+      <c r="BN304">
+        <v>1.53</v>
+      </c>
+      <c r="BO304">
+        <v>2.97</v>
+      </c>
+      <c r="BP304">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="409">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -844,9 +844,6 @@
     <t>['11', '45+4']</t>
   </si>
   <si>
-    <t>['34', '90']</t>
-  </si>
-  <si>
     <t>['83']</t>
   </si>
   <si>
@@ -854,6 +851,9 @@
   </si>
   <si>
     <t>['41', '52', '85']</t>
+  </si>
+  <si>
+    <t>['34', '90']</t>
   </si>
   <si>
     <t>['45+2']</t>
@@ -1210,31 +1210,31 @@
     <t>['18', '30', '61']</t>
   </si>
   <si>
-    <t>['12', '39']</t>
+    <t>['88', '90+1']</t>
   </si>
   <si>
-    <t>['88', '90+1']</t>
+    <t>['12', '39']</t>
   </si>
   <si>
     <t>['47', '50']</t>
   </si>
   <si>
-    <t>['4', '36']</t>
-  </si>
-  <si>
-    <t>['25']</t>
+    <t>['55', '90+5']</t>
   </si>
   <si>
     <t>['57', '87']</t>
   </si>
   <si>
-    <t>['55', '90+5']</t>
+    <t>['25']</t>
   </si>
   <si>
     <t>['45', '90+2']</t>
   </si>
   <si>
     <t>['5', '13', '68']</t>
+  </si>
+  <si>
+    <t>['4', '36']</t>
   </si>
   <si>
     <t>['71', '86']</t>
@@ -1602,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP304"/>
+  <dimension ref="A1:BP305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ3">
         <v>2.14</v>
@@ -5235,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -7498,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ29">
         <v>1.08</v>
@@ -9149,7 +9149,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ37">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR37">
         <v>1.32</v>
@@ -12030,7 +12030,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ51">
         <v>0.5</v>
@@ -16562,7 +16562,7 @@
         <v>1.5</v>
       </c>
       <c r="AP73">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ73">
         <v>0.6899999999999999</v>
@@ -17183,7 +17183,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ76">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR76">
         <v>1.79</v>
@@ -25011,7 +25011,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ114">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR114">
         <v>1.26</v>
@@ -25214,7 +25214,7 @@
         <v>1.33</v>
       </c>
       <c r="AP115">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ115">
         <v>0.79</v>
@@ -26659,7 +26659,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR122">
         <v>1.41</v>
@@ -30158,7 +30158,7 @@
         <v>1.2</v>
       </c>
       <c r="AP139">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ139">
         <v>1.75</v>
@@ -30779,7 +30779,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ142">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR142">
         <v>1.27</v>
@@ -34484,7 +34484,7 @@
         <v>2.4</v>
       </c>
       <c r="AP160">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ160">
         <v>1.58</v>
@@ -37989,7 +37989,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ177">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR177">
         <v>0.99</v>
@@ -39428,7 +39428,7 @@
         <v>1.43</v>
       </c>
       <c r="AP184">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ184">
         <v>1.08</v>
@@ -40458,7 +40458,7 @@
         <v>1.63</v>
       </c>
       <c r="AP189">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ189">
         <v>1.21</v>
@@ -41285,7 +41285,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ193">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR193">
         <v>1.36</v>
@@ -42724,7 +42724,7 @@
         <v>2</v>
       </c>
       <c r="AP200">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ200">
         <v>1.92</v>
@@ -44993,7 +44993,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ211">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR211">
         <v>1.76</v>
@@ -48080,7 +48080,7 @@
         <v>0.44</v>
       </c>
       <c r="AP226">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ226">
         <v>0.46</v>
@@ -51173,7 +51173,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ241">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR241">
         <v>0.97</v>
@@ -53024,7 +53024,7 @@
         <v>1.45</v>
       </c>
       <c r="AP250">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ250">
         <v>1.29</v>
@@ -55908,7 +55908,7 @@
         <v>1.36</v>
       </c>
       <c r="AP264">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ264">
         <v>1.38</v>
@@ -56529,7 +56529,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ267">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR267">
         <v>1.61</v>
@@ -58998,7 +58998,7 @@
         <v>0.8</v>
       </c>
       <c r="AP279">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AQ279">
         <v>0.73</v>
@@ -59207,7 +59207,7 @@
         <v>1</v>
       </c>
       <c r="AQ280">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AR280">
         <v>1.16</v>
@@ -59290,7 +59290,7 @@
         <v>280</v>
       </c>
       <c r="B281">
-        <v>7727147</v>
+        <v>7727146</v>
       </c>
       <c r="C281" t="s">
         <v>68</v>
@@ -59305,160 +59305,160 @@
         <v>25</v>
       </c>
       <c r="G281" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H281" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I281">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K281">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L281">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N281">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O281" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="P281" t="s">
-        <v>398</v>
+        <v>96</v>
       </c>
       <c r="Q281">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R281">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S281">
         <v>4.5</v>
       </c>
       <c r="T281">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U281">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V281">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="W281">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X281">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y281">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z281">
+        <v>2</v>
+      </c>
+      <c r="AA281">
+        <v>3.1</v>
+      </c>
+      <c r="AB281">
+        <v>3.75</v>
+      </c>
+      <c r="AC281">
+        <v>1.08</v>
+      </c>
+      <c r="AD281">
+        <v>7.5</v>
+      </c>
+      <c r="AE281">
+        <v>1.5</v>
+      </c>
+      <c r="AF281">
+        <v>2.4</v>
+      </c>
+      <c r="AG281">
+        <v>2.1</v>
+      </c>
+      <c r="AH281">
+        <v>1.65</v>
+      </c>
+      <c r="AI281">
         <v>1.95</v>
       </c>
-      <c r="AA281">
-        <v>3.5</v>
-      </c>
-      <c r="AB281">
-        <v>3.4</v>
-      </c>
-      <c r="AC281">
+      <c r="AJ281">
+        <v>1.8</v>
+      </c>
+      <c r="AK281">
+        <v>1.22</v>
+      </c>
+      <c r="AL281">
+        <v>1.25</v>
+      </c>
+      <c r="AM281">
+        <v>1.8</v>
+      </c>
+      <c r="AN281">
+        <v>1.55</v>
+      </c>
+      <c r="AO281">
+        <v>0.78</v>
+      </c>
+      <c r="AP281">
+        <v>1.5</v>
+      </c>
+      <c r="AQ281">
+        <v>0.8</v>
+      </c>
+      <c r="AR281">
+        <v>1.32</v>
+      </c>
+      <c r="AS281">
         <v>1.04</v>
       </c>
-      <c r="AD281">
-        <v>11</v>
-      </c>
-      <c r="AE281">
-        <v>1.3</v>
-      </c>
-      <c r="AF281">
-        <v>3.4</v>
-      </c>
-      <c r="AG281">
-        <v>1.91</v>
-      </c>
-      <c r="AH281">
-        <v>1.8</v>
-      </c>
-      <c r="AI281">
-        <v>1.91</v>
-      </c>
-      <c r="AJ281">
-        <v>1.91</v>
-      </c>
-      <c r="AK281">
-        <v>1.26</v>
-      </c>
-      <c r="AL281">
-        <v>1.29</v>
-      </c>
-      <c r="AM281">
-        <v>1.82</v>
-      </c>
-      <c r="AN281">
-        <v>2</v>
-      </c>
-      <c r="AO281">
-        <v>1.45</v>
-      </c>
-      <c r="AP281">
-        <v>1.85</v>
-      </c>
-      <c r="AQ281">
-        <v>1.58</v>
-      </c>
-      <c r="AR281">
-        <v>1.62</v>
-      </c>
-      <c r="AS281">
-        <v>1.25</v>
-      </c>
       <c r="AT281">
-        <v>2.87</v>
+        <v>2.36</v>
       </c>
       <c r="AU281">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV281">
         <v>5</v>
       </c>
       <c r="AW281">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX281">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY281">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ281">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA281">
         <v>7</v>
       </c>
       <c r="BB281">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC281">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD281">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BE281">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="BF281">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="BG281">
         <v>1.27</v>
@@ -59467,28 +59467,28 @@
         <v>3.3</v>
       </c>
       <c r="BI281">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="BJ281">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BK281">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="BL281">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="BM281">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="BN281">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="BO281">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="BP281">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="282" spans="1:68">
@@ -59496,7 +59496,7 @@
         <v>281</v>
       </c>
       <c r="B282">
-        <v>7727146</v>
+        <v>7727145</v>
       </c>
       <c r="C282" t="s">
         <v>68</v>
@@ -59511,10 +59511,10 @@
         <v>25</v>
       </c>
       <c r="G282" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="H282" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I282">
         <v>0</v>
@@ -59526,175 +59526,175 @@
         <v>0</v>
       </c>
       <c r="L282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M282">
         <v>0</v>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O282" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="P282" t="s">
         <v>96</v>
       </c>
       <c r="Q282">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="R282">
+        <v>2.2</v>
+      </c>
+      <c r="S282">
+        <v>6</v>
+      </c>
+      <c r="T282">
+        <v>1.4</v>
+      </c>
+      <c r="U282">
+        <v>2.75</v>
+      </c>
+      <c r="V282">
+        <v>3</v>
+      </c>
+      <c r="W282">
+        <v>1.36</v>
+      </c>
+      <c r="X282">
+        <v>8</v>
+      </c>
+      <c r="Y282">
+        <v>1.08</v>
+      </c>
+      <c r="Z282">
+        <v>1.5</v>
+      </c>
+      <c r="AA282">
+        <v>4</v>
+      </c>
+      <c r="AB282">
+        <v>5.75</v>
+      </c>
+      <c r="AC282">
+        <v>1.05</v>
+      </c>
+      <c r="AD282">
+        <v>9</v>
+      </c>
+      <c r="AE282">
+        <v>1.3</v>
+      </c>
+      <c r="AF282">
+        <v>3.35</v>
+      </c>
+      <c r="AG282">
+        <v>2</v>
+      </c>
+      <c r="AH282">
+        <v>1.73</v>
+      </c>
+      <c r="AI282">
         <v>2.05</v>
       </c>
-      <c r="S282">
-        <v>4.5</v>
-      </c>
-      <c r="T282">
+      <c r="AJ282">
+        <v>1.7</v>
+      </c>
+      <c r="AK282">
+        <v>1.12</v>
+      </c>
+      <c r="AL282">
+        <v>1.2</v>
+      </c>
+      <c r="AM282">
+        <v>2.4</v>
+      </c>
+      <c r="AN282">
         <v>1.5</v>
       </c>
-      <c r="U282">
-        <v>2.5</v>
-      </c>
-      <c r="V282">
-        <v>3.4</v>
-      </c>
-      <c r="W282">
+      <c r="AO282">
+        <v>0.55</v>
+      </c>
+      <c r="AP282">
+        <v>1.62</v>
+      </c>
+      <c r="AQ282">
+        <v>0.5</v>
+      </c>
+      <c r="AR282">
+        <v>1.5</v>
+      </c>
+      <c r="AS282">
+        <v>1.11</v>
+      </c>
+      <c r="AT282">
+        <v>2.61</v>
+      </c>
+      <c r="AU282">
+        <v>6</v>
+      </c>
+      <c r="AV282">
+        <v>0</v>
+      </c>
+      <c r="AW282">
+        <v>6</v>
+      </c>
+      <c r="AX282">
+        <v>6</v>
+      </c>
+      <c r="AY282">
+        <v>14</v>
+      </c>
+      <c r="AZ282">
+        <v>9</v>
+      </c>
+      <c r="BA282">
+        <v>9</v>
+      </c>
+      <c r="BB282">
+        <v>7</v>
+      </c>
+      <c r="BC282">
+        <v>16</v>
+      </c>
+      <c r="BD282">
+        <v>1.32</v>
+      </c>
+      <c r="BE282">
+        <v>7.5</v>
+      </c>
+      <c r="BF282">
+        <v>3.7</v>
+      </c>
+      <c r="BG282">
         <v>1.3</v>
       </c>
-      <c r="X282">
-        <v>10</v>
-      </c>
-      <c r="Y282">
-        <v>1.06</v>
-      </c>
-      <c r="Z282">
-        <v>2</v>
-      </c>
-      <c r="AA282">
-        <v>3.1</v>
-      </c>
-      <c r="AB282">
-        <v>3.75</v>
-      </c>
-      <c r="AC282">
-        <v>1.08</v>
-      </c>
-      <c r="AD282">
-        <v>7.5</v>
-      </c>
-      <c r="AE282">
+      <c r="BH282">
+        <v>3.15</v>
+      </c>
+      <c r="BI282">
         <v>1.5</v>
       </c>
-      <c r="AF282">
-        <v>2.4</v>
-      </c>
-      <c r="AG282">
-        <v>2.1</v>
-      </c>
-      <c r="AH282">
-        <v>1.65</v>
-      </c>
-      <c r="AI282">
-        <v>1.95</v>
-      </c>
-      <c r="AJ282">
-        <v>1.8</v>
-      </c>
-      <c r="AK282">
-        <v>1.22</v>
-      </c>
-      <c r="AL282">
-        <v>1.25</v>
-      </c>
-      <c r="AM282">
-        <v>1.8</v>
-      </c>
-      <c r="AN282">
+      <c r="BJ282">
+        <v>2.38</v>
+      </c>
+      <c r="BK282">
+        <v>1.81</v>
+      </c>
+      <c r="BL282">
+        <v>1.88</v>
+      </c>
+      <c r="BM282">
+        <v>2.25</v>
+      </c>
+      <c r="BN282">
         <v>1.55</v>
       </c>
-      <c r="AO282">
-        <v>0.78</v>
-      </c>
-      <c r="AP282">
-        <v>1.5</v>
-      </c>
-      <c r="AQ282">
-        <v>0.8</v>
-      </c>
-      <c r="AR282">
-        <v>1.32</v>
-      </c>
-      <c r="AS282">
-        <v>1.04</v>
-      </c>
-      <c r="AT282">
-        <v>2.36</v>
-      </c>
-      <c r="AU282">
-        <v>4</v>
-      </c>
-      <c r="AV282">
-        <v>5</v>
-      </c>
-      <c r="AW282">
-        <v>2</v>
-      </c>
-      <c r="AX282">
-        <v>3</v>
-      </c>
-      <c r="AY282">
-        <v>9</v>
-      </c>
-      <c r="AZ282">
-        <v>12</v>
-      </c>
-      <c r="BA282">
-        <v>7</v>
-      </c>
-      <c r="BB282">
-        <v>6</v>
-      </c>
-      <c r="BC282">
-        <v>13</v>
-      </c>
-      <c r="BD282">
-        <v>1.71</v>
-      </c>
-      <c r="BE282">
-        <v>6.75</v>
-      </c>
-      <c r="BF282">
-        <v>2.35</v>
-      </c>
-      <c r="BG282">
-        <v>1.27</v>
-      </c>
-      <c r="BH282">
-        <v>3.3</v>
-      </c>
-      <c r="BI282">
-        <v>1.48</v>
-      </c>
-      <c r="BJ282">
-        <v>2.45</v>
-      </c>
-      <c r="BK282">
-        <v>1.75</v>
-      </c>
-      <c r="BL282">
-        <v>1.95</v>
-      </c>
-      <c r="BM282">
-        <v>2.17</v>
-      </c>
-      <c r="BN282">
-        <v>1.6</v>
-      </c>
       <c r="BO282">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="BP282">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="283" spans="1:68">
@@ -59702,7 +59702,7 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>7727145</v>
+        <v>7727144</v>
       </c>
       <c r="C283" t="s">
         <v>68</v>
@@ -59717,10 +59717,10 @@
         <v>25</v>
       </c>
       <c r="G283" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H283" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I283">
         <v>0</v>
@@ -59732,175 +59732,175 @@
         <v>0</v>
       </c>
       <c r="L283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M283">
         <v>0</v>
       </c>
       <c r="N283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O283" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="P283" t="s">
         <v>96</v>
       </c>
       <c r="Q283">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R283">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S283">
+        <v>5.5</v>
+      </c>
+      <c r="T283">
+        <v>1.44</v>
+      </c>
+      <c r="U283">
+        <v>2.63</v>
+      </c>
+      <c r="V283">
+        <v>3.25</v>
+      </c>
+      <c r="W283">
+        <v>1.33</v>
+      </c>
+      <c r="X283">
+        <v>9</v>
+      </c>
+      <c r="Y283">
+        <v>1.07</v>
+      </c>
+      <c r="Z283">
+        <v>1.73</v>
+      </c>
+      <c r="AA283">
+        <v>3.6</v>
+      </c>
+      <c r="AB283">
+        <v>4.33</v>
+      </c>
+      <c r="AC283">
+        <v>1.07</v>
+      </c>
+      <c r="AD283">
+        <v>8</v>
+      </c>
+      <c r="AE283">
+        <v>1.36</v>
+      </c>
+      <c r="AF283">
+        <v>3.1</v>
+      </c>
+      <c r="AG283">
+        <v>2.1</v>
+      </c>
+      <c r="AH283">
+        <v>1.67</v>
+      </c>
+      <c r="AI283">
+        <v>2</v>
+      </c>
+      <c r="AJ283">
+        <v>1.75</v>
+      </c>
+      <c r="AK283">
+        <v>1.15</v>
+      </c>
+      <c r="AL283">
+        <v>1.22</v>
+      </c>
+      <c r="AM283">
+        <v>2.1</v>
+      </c>
+      <c r="AN283">
+        <v>2.17</v>
+      </c>
+      <c r="AO283">
+        <v>0.82</v>
+      </c>
+      <c r="AP283">
+        <v>2.08</v>
+      </c>
+      <c r="AQ283">
+        <v>0.83</v>
+      </c>
+      <c r="AR283">
+        <v>1.41</v>
+      </c>
+      <c r="AS283">
+        <v>1.33</v>
+      </c>
+      <c r="AT283">
+        <v>2.74</v>
+      </c>
+      <c r="AU283">
+        <v>10</v>
+      </c>
+      <c r="AV283">
+        <v>4</v>
+      </c>
+      <c r="AW283">
+        <v>7</v>
+      </c>
+      <c r="AX283">
+        <v>4</v>
+      </c>
+      <c r="AY283">
+        <v>25</v>
+      </c>
+      <c r="AZ283">
+        <v>12</v>
+      </c>
+      <c r="BA283">
         <v>6</v>
       </c>
-      <c r="T283">
-        <v>1.4</v>
-      </c>
-      <c r="U283">
-        <v>2.75</v>
-      </c>
-      <c r="V283">
-        <v>3</v>
-      </c>
-      <c r="W283">
-        <v>1.36</v>
-      </c>
-      <c r="X283">
-        <v>8</v>
-      </c>
-      <c r="Y283">
-        <v>1.08</v>
-      </c>
-      <c r="Z283">
-        <v>1.5</v>
-      </c>
-      <c r="AA283">
-        <v>4</v>
-      </c>
-      <c r="AB283">
-        <v>5.75</v>
-      </c>
-      <c r="AC283">
-        <v>1.05</v>
-      </c>
-      <c r="AD283">
+      <c r="BB283">
+        <v>3</v>
+      </c>
+      <c r="BC283">
         <v>9</v>
       </c>
-      <c r="AE283">
-        <v>1.3</v>
-      </c>
-      <c r="AF283">
-        <v>3.35</v>
-      </c>
-      <c r="AG283">
-        <v>2</v>
-      </c>
-      <c r="AH283">
-        <v>1.73</v>
-      </c>
-      <c r="AI283">
-        <v>2.05</v>
-      </c>
-      <c r="AJ283">
-        <v>1.7</v>
-      </c>
-      <c r="AK283">
-        <v>1.12</v>
-      </c>
-      <c r="AL283">
-        <v>1.2</v>
-      </c>
-      <c r="AM283">
-        <v>2.4</v>
-      </c>
-      <c r="AN283">
-        <v>1.5</v>
-      </c>
-      <c r="AO283">
-        <v>0.55</v>
-      </c>
-      <c r="AP283">
-        <v>1.62</v>
-      </c>
-      <c r="AQ283">
-        <v>0.5</v>
-      </c>
-      <c r="AR283">
-        <v>1.5</v>
-      </c>
-      <c r="AS283">
-        <v>1.11</v>
-      </c>
-      <c r="AT283">
-        <v>2.61</v>
-      </c>
-      <c r="AU283">
-        <v>6</v>
-      </c>
-      <c r="AV283">
-        <v>0</v>
-      </c>
-      <c r="AW283">
-        <v>6</v>
-      </c>
-      <c r="AX283">
-        <v>6</v>
-      </c>
-      <c r="AY283">
-        <v>14</v>
-      </c>
-      <c r="AZ283">
-        <v>9</v>
-      </c>
-      <c r="BA283">
-        <v>9</v>
-      </c>
-      <c r="BB283">
+      <c r="BD283">
+        <v>1.48</v>
+      </c>
+      <c r="BE283">
         <v>7</v>
       </c>
-      <c r="BC283">
-        <v>16</v>
-      </c>
-      <c r="BD283">
-        <v>1.32</v>
-      </c>
-      <c r="BE283">
-        <v>7.5</v>
-      </c>
       <c r="BF283">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="BG283">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="BH283">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BI283">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BJ283">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="BK283">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="BL283">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="BM283">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="BN283">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="BO283">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="BP283">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="284" spans="1:68">
@@ -59950,7 +59950,7 @@
         <v>172</v>
       </c>
       <c r="P284" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60526,7 +60526,7 @@
         <v>286</v>
       </c>
       <c r="B287">
-        <v>7727144</v>
+        <v>7727147</v>
       </c>
       <c r="C287" t="s">
         <v>68</v>
@@ -60541,43 +60541,43 @@
         <v>25</v>
       </c>
       <c r="G287" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="H287" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K287">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O287" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="P287" t="s">
-        <v>96</v>
+        <v>399</v>
       </c>
       <c r="Q287">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="R287">
         <v>2.1</v>
       </c>
       <c r="S287">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="T287">
         <v>1.44</v>
@@ -60586,10 +60586,10 @@
         <v>2.63</v>
       </c>
       <c r="V287">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="W287">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X287">
         <v>9</v>
@@ -60598,133 +60598,133 @@
         <v>1.07</v>
       </c>
       <c r="Z287">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AA287">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB287">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AC287">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AD287">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE287">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF287">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AG287">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH287">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI287">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ287">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AK287">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AL287">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AM287">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AN287">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AO287">
-        <v>0.82</v>
+        <v>1.45</v>
       </c>
       <c r="AP287">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AQ287">
-        <v>0.83</v>
+        <v>1.58</v>
       </c>
       <c r="AR287">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AS287">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT287">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AU287">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AV287">
+        <v>5</v>
+      </c>
+      <c r="AW287">
         <v>4</v>
-      </c>
-      <c r="AW287">
-        <v>7</v>
       </c>
       <c r="AX287">
         <v>4</v>
       </c>
       <c r="AY287">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AZ287">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA287">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB287">
         <v>3</v>
       </c>
       <c r="BC287">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD287">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BE287">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="BF287">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BG287">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BH287">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI287">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="BJ287">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="BK287">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="BL287">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="BM287">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="BN287">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="BO287">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP287">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="288" spans="1:68">
@@ -61350,7 +61350,7 @@
         <v>290</v>
       </c>
       <c r="B291">
-        <v>7727169</v>
+        <v>7727163</v>
       </c>
       <c r="C291" t="s">
         <v>68</v>
@@ -61365,190 +61365,190 @@
         <v>27</v>
       </c>
       <c r="G291" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="H291" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J291">
         <v>0</v>
       </c>
       <c r="K291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O291" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="P291" t="s">
-        <v>96</v>
+        <v>400</v>
       </c>
       <c r="Q291">
         <v>3.4</v>
       </c>
       <c r="R291">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S291">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T291">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U291">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="V291">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="W291">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X291">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Y291">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z291">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AA291">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AB291">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AC291">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD291">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE291">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF291">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AG291">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AH291">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AI291">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AJ291">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AK291">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL291">
         <v>1.25</v>
       </c>
       <c r="AM291">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AN291">
+        <v>1.2</v>
+      </c>
+      <c r="AO291">
+        <v>1.82</v>
+      </c>
+      <c r="AP291">
+        <v>1.18</v>
+      </c>
+      <c r="AQ291">
+        <v>1.75</v>
+      </c>
+      <c r="AR291">
+        <v>1.55</v>
+      </c>
+      <c r="AS291">
         <v>1.31</v>
       </c>
-      <c r="AO291">
-        <v>1.45</v>
-      </c>
-      <c r="AP291">
-        <v>1.27</v>
-      </c>
-      <c r="AQ291">
-        <v>1.42</v>
-      </c>
-      <c r="AR291">
-        <v>1.23</v>
-      </c>
-      <c r="AS291">
-        <v>1</v>
-      </c>
       <c r="AT291">
-        <v>2.23</v>
+        <v>2.86</v>
       </c>
       <c r="AU291">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV291">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AW291">
+        <v>7</v>
+      </c>
+      <c r="AX291">
+        <v>12</v>
+      </c>
+      <c r="AY291">
+        <v>15</v>
+      </c>
+      <c r="AZ291">
+        <v>22</v>
+      </c>
+      <c r="BA291">
         <v>5</v>
       </c>
-      <c r="AX291">
-        <v>10</v>
-      </c>
-      <c r="AY291">
-        <v>13</v>
-      </c>
-      <c r="AZ291">
-        <v>18</v>
-      </c>
-      <c r="BA291">
-        <v>4</v>
-      </c>
       <c r="BB291">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BC291">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD291">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BE291">
         <v>6.75</v>
       </c>
       <c r="BF291">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="BG291">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BH291">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI291">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BJ291">
+        <v>2.65</v>
+      </c>
+      <c r="BK291">
+        <v>1.67</v>
+      </c>
+      <c r="BL291">
+        <v>2.04</v>
+      </c>
+      <c r="BM291">
+        <v>2.07</v>
+      </c>
+      <c r="BN291">
+        <v>1.65</v>
+      </c>
+      <c r="BO291">
         <v>2.55</v>
       </c>
-      <c r="BK291">
-        <v>1.72</v>
-      </c>
-      <c r="BL291">
-        <v>1.98</v>
-      </c>
-      <c r="BM291">
-        <v>2.1</v>
-      </c>
-      <c r="BN291">
-        <v>1.64</v>
-      </c>
-      <c r="BO291">
-        <v>2.65</v>
-      </c>
       <c r="BP291">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="292" spans="1:68">
@@ -61556,7 +61556,7 @@
         <v>291</v>
       </c>
       <c r="B292">
-        <v>7727163</v>
+        <v>7727169</v>
       </c>
       <c r="C292" t="s">
         <v>68</v>
@@ -61571,190 +61571,190 @@
         <v>27</v>
       </c>
       <c r="G292" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H292" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I292">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J292">
         <v>0</v>
       </c>
       <c r="K292">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L292">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M292">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N292">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O292" t="s">
-        <v>275</v>
+        <v>96</v>
       </c>
       <c r="P292" t="s">
-        <v>400</v>
+        <v>96</v>
       </c>
       <c r="Q292">
         <v>3.4</v>
       </c>
       <c r="R292">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S292">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T292">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U292">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="V292">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W292">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X292">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y292">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z292">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA292">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="AB292">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AC292">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD292">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE292">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF292">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG292">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AH292">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AI292">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AJ292">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AK292">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL292">
         <v>1.25</v>
       </c>
       <c r="AM292">
+        <v>1.45</v>
+      </c>
+      <c r="AN292">
+        <v>1.31</v>
+      </c>
+      <c r="AO292">
+        <v>1.45</v>
+      </c>
+      <c r="AP292">
+        <v>1.27</v>
+      </c>
+      <c r="AQ292">
         <v>1.42</v>
       </c>
-      <c r="AN292">
-        <v>1.2</v>
-      </c>
-      <c r="AO292">
-        <v>1.82</v>
-      </c>
-      <c r="AP292">
-        <v>1.18</v>
-      </c>
-      <c r="AQ292">
-        <v>1.75</v>
-      </c>
       <c r="AR292">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="AS292">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AT292">
-        <v>2.86</v>
+        <v>2.23</v>
       </c>
       <c r="AU292">
+        <v>4</v>
+      </c>
+      <c r="AV292">
+        <v>2</v>
+      </c>
+      <c r="AW292">
         <v>5</v>
       </c>
-      <c r="AV292">
-        <v>7</v>
-      </c>
-      <c r="AW292">
-        <v>7</v>
-      </c>
       <c r="AX292">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY292">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ292">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA292">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB292">
+        <v>2</v>
+      </c>
+      <c r="BC292">
         <v>6</v>
       </c>
-      <c r="BC292">
-        <v>11</v>
-      </c>
       <c r="BD292">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BE292">
         <v>6.75</v>
       </c>
       <c r="BF292">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="BG292">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BH292">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BI292">
+        <v>1.44</v>
+      </c>
+      <c r="BJ292">
+        <v>2.55</v>
+      </c>
+      <c r="BK292">
+        <v>1.72</v>
+      </c>
+      <c r="BL292">
+        <v>1.98</v>
+      </c>
+      <c r="BM292">
+        <v>2.1</v>
+      </c>
+      <c r="BN292">
+        <v>1.64</v>
+      </c>
+      <c r="BO292">
+        <v>2.65</v>
+      </c>
+      <c r="BP292">
         <v>1.41</v>
-      </c>
-      <c r="BJ292">
-        <v>2.65</v>
-      </c>
-      <c r="BK292">
-        <v>1.67</v>
-      </c>
-      <c r="BL292">
-        <v>2.04</v>
-      </c>
-      <c r="BM292">
-        <v>2.07</v>
-      </c>
-      <c r="BN292">
-        <v>1.65</v>
-      </c>
-      <c r="BO292">
-        <v>2.55</v>
-      </c>
-      <c r="BP292">
-        <v>1.43</v>
       </c>
     </row>
     <row r="293" spans="1:68">
@@ -61968,7 +61968,7 @@
         <v>293</v>
       </c>
       <c r="B294">
-        <v>7727164</v>
+        <v>7727173</v>
       </c>
       <c r="C294" t="s">
         <v>68</v>
@@ -61983,28 +61983,28 @@
         <v>27</v>
       </c>
       <c r="G294" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H294" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K294">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M294">
         <v>2</v>
       </c>
       <c r="N294">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O294" t="s">
         <v>276</v>
@@ -62013,160 +62013,160 @@
         <v>401</v>
       </c>
       <c r="Q294">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="R294">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="S294">
+        <v>4.33</v>
+      </c>
+      <c r="T294">
+        <v>1.57</v>
+      </c>
+      <c r="U294">
+        <v>2.25</v>
+      </c>
+      <c r="V294">
+        <v>3.75</v>
+      </c>
+      <c r="W294">
+        <v>1.25</v>
+      </c>
+      <c r="X294">
+        <v>13</v>
+      </c>
+      <c r="Y294">
+        <v>1.04</v>
+      </c>
+      <c r="Z294">
+        <v>2.15</v>
+      </c>
+      <c r="AA294">
+        <v>2.85</v>
+      </c>
+      <c r="AB294">
+        <v>3.07</v>
+      </c>
+      <c r="AC294">
+        <v>1.1</v>
+      </c>
+      <c r="AD294">
+        <v>6.5</v>
+      </c>
+      <c r="AE294">
+        <v>1.5</v>
+      </c>
+      <c r="AF294">
+        <v>2.4</v>
+      </c>
+      <c r="AG294">
+        <v>2.47</v>
+      </c>
+      <c r="AH294">
+        <v>1.48</v>
+      </c>
+      <c r="AI294">
+        <v>2.2</v>
+      </c>
+      <c r="AJ294">
+        <v>1.62</v>
+      </c>
+      <c r="AK294">
+        <v>1.3</v>
+      </c>
+      <c r="AL294">
+        <v>1.3</v>
+      </c>
+      <c r="AM294">
+        <v>1.62</v>
+      </c>
+      <c r="AN294">
+        <v>1.77</v>
+      </c>
+      <c r="AO294">
+        <v>1.25</v>
+      </c>
+      <c r="AP294">
+        <v>1.64</v>
+      </c>
+      <c r="AQ294">
+        <v>1.38</v>
+      </c>
+      <c r="AR294">
+        <v>1.13</v>
+      </c>
+      <c r="AS294">
+        <v>1.1</v>
+      </c>
+      <c r="AT294">
+        <v>2.23</v>
+      </c>
+      <c r="AU294">
+        <v>5</v>
+      </c>
+      <c r="AV294">
         <v>6</v>
       </c>
-      <c r="T294">
-        <v>1.33</v>
-      </c>
-      <c r="U294">
-        <v>3.25</v>
-      </c>
-      <c r="V294">
-        <v>2.63</v>
-      </c>
-      <c r="W294">
-        <v>1.44</v>
-      </c>
-      <c r="X294">
-        <v>6.5</v>
-      </c>
-      <c r="Y294">
-        <v>1.11</v>
-      </c>
-      <c r="Z294">
-        <v>1.42</v>
-      </c>
-      <c r="AA294">
-        <v>3.86</v>
-      </c>
-      <c r="AB294">
-        <v>5.5</v>
-      </c>
-      <c r="AC294">
-        <v>1.04</v>
-      </c>
-      <c r="AD294">
+      <c r="AW294">
         <v>10</v>
       </c>
-      <c r="AE294">
-        <v>1.22</v>
-      </c>
-      <c r="AF294">
-        <v>4.2</v>
-      </c>
-      <c r="AG294">
-        <v>1.79</v>
-      </c>
-      <c r="AH294">
-        <v>1.91</v>
-      </c>
-      <c r="AI294">
-        <v>1.8</v>
-      </c>
-      <c r="AJ294">
+      <c r="AX294">
+        <v>3</v>
+      </c>
+      <c r="AY294">
+        <v>18</v>
+      </c>
+      <c r="AZ294">
+        <v>9</v>
+      </c>
+      <c r="BA294">
+        <v>3</v>
+      </c>
+      <c r="BB294">
+        <v>3</v>
+      </c>
+      <c r="BC294">
+        <v>6</v>
+      </c>
+      <c r="BD294">
+        <v>1.57</v>
+      </c>
+      <c r="BE294">
+        <v>6.75</v>
+      </c>
+      <c r="BF294">
+        <v>2.65</v>
+      </c>
+      <c r="BG294">
+        <v>1.34</v>
+      </c>
+      <c r="BH294">
+        <v>2.9</v>
+      </c>
+      <c r="BI294">
+        <v>1.58</v>
+      </c>
+      <c r="BJ294">
+        <v>2.2</v>
+      </c>
+      <c r="BK294">
         <v>1.95</v>
       </c>
-      <c r="AK294">
-        <v>1.12</v>
-      </c>
-      <c r="AL294">
-        <v>1.17</v>
-      </c>
-      <c r="AM294">
-        <v>2.55</v>
-      </c>
-      <c r="AN294">
-        <v>1.67</v>
-      </c>
-      <c r="AO294">
-        <v>0.42</v>
-      </c>
-      <c r="AP294">
-        <v>1.5</v>
-      </c>
-      <c r="AQ294">
-        <v>0.46</v>
-      </c>
-      <c r="AR294">
-        <v>1.64</v>
-      </c>
-      <c r="AS294">
-        <v>1.15</v>
-      </c>
-      <c r="AT294">
-        <v>2.79</v>
-      </c>
-      <c r="AU294">
-        <v>6</v>
-      </c>
-      <c r="AV294">
-        <v>3</v>
-      </c>
-      <c r="AW294">
-        <v>13</v>
-      </c>
-      <c r="AX294">
-        <v>3</v>
-      </c>
-      <c r="AY294">
-        <v>19</v>
-      </c>
-      <c r="AZ294">
-        <v>6</v>
-      </c>
-      <c r="BA294">
-        <v>5</v>
-      </c>
-      <c r="BB294">
-        <v>0</v>
-      </c>
-      <c r="BC294">
-        <v>5</v>
-      </c>
-      <c r="BD294">
-        <v>1.35</v>
-      </c>
-      <c r="BE294">
-        <v>7.5</v>
-      </c>
-      <c r="BF294">
-        <v>3.45</v>
-      </c>
-      <c r="BG294">
-        <v>1.24</v>
-      </c>
-      <c r="BH294">
-        <v>3.55</v>
-      </c>
-      <c r="BI294">
-        <v>1.41</v>
-      </c>
-      <c r="BJ294">
-        <v>2.65</v>
-      </c>
-      <c r="BK294">
-        <v>1.67</v>
-      </c>
       <c r="BL294">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="BM294">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="BN294">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="BO294">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="BP294">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="295" spans="1:68">
@@ -62174,7 +62174,7 @@
         <v>294</v>
       </c>
       <c r="B295">
-        <v>7727166</v>
+        <v>7727167</v>
       </c>
       <c r="C295" t="s">
         <v>68</v>
@@ -62189,43 +62189,43 @@
         <v>27</v>
       </c>
       <c r="G295" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="H295" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I295">
         <v>0</v>
       </c>
       <c r="J295">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K295">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L295">
         <v>1</v>
       </c>
       <c r="M295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N295">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O295" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="P295" t="s">
         <v>402</v>
       </c>
       <c r="Q295">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="R295">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S295">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T295">
         <v>1.4</v>
@@ -62234,10 +62234,10 @@
         <v>2.75</v>
       </c>
       <c r="V295">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W295">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X295">
         <v>8</v>
@@ -62246,19 +62246,19 @@
         <v>1.08</v>
       </c>
       <c r="Z295">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA295">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="AB295">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="AC295">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD295">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AE295">
         <v>1.3</v>
@@ -62267,112 +62267,112 @@
         <v>3.4</v>
       </c>
       <c r="AG295">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH295">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AI295">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AJ295">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AK295">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AL295">
         <v>1.25</v>
       </c>
       <c r="AM295">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AN295">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="AO295">
-        <v>0.73</v>
+        <v>2.08</v>
       </c>
       <c r="AP295">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="AQ295">
-        <v>0.92</v>
+        <v>2.14</v>
       </c>
       <c r="AR295">
-        <v>0.91</v>
+        <v>1.37</v>
       </c>
       <c r="AS295">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AT295">
-        <v>1.97</v>
+        <v>2.79</v>
       </c>
       <c r="AU295">
         <v>5</v>
       </c>
       <c r="AV295">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW295">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX295">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AY295">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ295">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BA295">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB295">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC295">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD295">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="BE295">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF295">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="BG295">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BH295">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="BI295">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BJ295">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="BK295">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BL295">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="BM295">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BN295">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO295">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="BP295">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="296" spans="1:68">
@@ -62380,7 +62380,7 @@
         <v>295</v>
       </c>
       <c r="B296">
-        <v>7727167</v>
+        <v>7727166</v>
       </c>
       <c r="C296" t="s">
         <v>68</v>
@@ -62395,43 +62395,43 @@
         <v>27</v>
       </c>
       <c r="G296" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="H296" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I296">
         <v>0</v>
       </c>
       <c r="J296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296">
         <v>1</v>
       </c>
       <c r="M296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N296">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O296" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="P296" t="s">
         <v>403</v>
       </c>
       <c r="Q296">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R296">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S296">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T296">
         <v>1.4</v>
@@ -62440,10 +62440,10 @@
         <v>2.75</v>
       </c>
       <c r="V296">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W296">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X296">
         <v>8</v>
@@ -62452,19 +62452,19 @@
         <v>1.08</v>
       </c>
       <c r="Z296">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA296">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="AB296">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="AC296">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD296">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE296">
         <v>1.3</v>
@@ -62473,112 +62473,112 @@
         <v>3.4</v>
       </c>
       <c r="AG296">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH296">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AI296">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AJ296">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AK296">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL296">
         <v>1.25</v>
       </c>
       <c r="AM296">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AN296">
-        <v>1.64</v>
+        <v>1.1</v>
       </c>
       <c r="AO296">
-        <v>2.08</v>
+        <v>0.73</v>
       </c>
       <c r="AP296">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AQ296">
-        <v>2.14</v>
+        <v>0.92</v>
       </c>
       <c r="AR296">
-        <v>1.37</v>
+        <v>0.91</v>
       </c>
       <c r="AS296">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="AT296">
-        <v>2.79</v>
+        <v>1.97</v>
       </c>
       <c r="AU296">
         <v>5</v>
       </c>
       <c r="AV296">
+        <v>3</v>
+      </c>
+      <c r="AW296">
+        <v>12</v>
+      </c>
+      <c r="AX296">
         <v>4</v>
       </c>
-      <c r="AW296">
-        <v>11</v>
-      </c>
-      <c r="AX296">
-        <v>13</v>
-      </c>
       <c r="AY296">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ296">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BA296">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB296">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC296">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD296">
+        <v>1.65</v>
+      </c>
+      <c r="BE296">
+        <v>6.75</v>
+      </c>
+      <c r="BF296">
+        <v>2.48</v>
+      </c>
+      <c r="BG296">
+        <v>1.33</v>
+      </c>
+      <c r="BH296">
+        <v>2.95</v>
+      </c>
+      <c r="BI296">
+        <v>1.56</v>
+      </c>
+      <c r="BJ296">
+        <v>2.23</v>
+      </c>
+      <c r="BK296">
+        <v>1.9</v>
+      </c>
+      <c r="BL296">
         <v>1.79</v>
       </c>
-      <c r="BE296">
-        <v>6.4</v>
-      </c>
-      <c r="BF296">
-        <v>2.23</v>
-      </c>
-      <c r="BG296">
-        <v>1.29</v>
-      </c>
-      <c r="BH296">
-        <v>3.2</v>
-      </c>
-      <c r="BI296">
+      <c r="BM296">
+        <v>2.38</v>
+      </c>
+      <c r="BN296">
         <v>1.5</v>
       </c>
-      <c r="BJ296">
-        <v>2.38</v>
-      </c>
-      <c r="BK296">
-        <v>1.82</v>
-      </c>
-      <c r="BL296">
-        <v>1.86</v>
-      </c>
-      <c r="BM296">
-        <v>2.28</v>
-      </c>
-      <c r="BN296">
-        <v>1.54</v>
-      </c>
       <c r="BO296">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BP296">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="297" spans="1:68">
@@ -62586,7 +62586,7 @@
         <v>296</v>
       </c>
       <c r="B297">
-        <v>7727173</v>
+        <v>7727171</v>
       </c>
       <c r="C297" t="s">
         <v>68</v>
@@ -62601,28 +62601,28 @@
         <v>27</v>
       </c>
       <c r="G297" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H297" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I297">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K297">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L297">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M297">
         <v>2</v>
       </c>
       <c r="N297">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O297" t="s">
         <v>277</v>
@@ -62631,160 +62631,160 @@
         <v>404</v>
       </c>
       <c r="Q297">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R297">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S297">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="T297">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U297">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V297">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="W297">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X297">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y297">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z297">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AA297">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="AB297">
-        <v>3.07</v>
+        <v>2.74</v>
       </c>
       <c r="AC297">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AD297">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE297">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF297">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AG297">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="AH297">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AI297">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ297">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AK297">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL297">
         <v>1.3</v>
       </c>
       <c r="AM297">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AN297">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AO297">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AP297">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AQ297">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AR297">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AS297">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AT297">
-        <v>2.23</v>
+        <v>2.79</v>
       </c>
       <c r="AU297">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV297">
         <v>6</v>
       </c>
       <c r="AW297">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX297">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY297">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AZ297">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA297">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB297">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC297">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD297">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="BE297">
         <v>6.75</v>
       </c>
       <c r="BF297">
+        <v>2.4</v>
+      </c>
+      <c r="BG297">
+        <v>1.25</v>
+      </c>
+      <c r="BH297">
+        <v>3.45</v>
+      </c>
+      <c r="BI297">
+        <v>1.44</v>
+      </c>
+      <c r="BJ297">
+        <v>2.55</v>
+      </c>
+      <c r="BK297">
+        <v>1.72</v>
+      </c>
+      <c r="BL297">
+        <v>1.98</v>
+      </c>
+      <c r="BM297">
+        <v>2.1</v>
+      </c>
+      <c r="BN297">
+        <v>1.64</v>
+      </c>
+      <c r="BO297">
         <v>2.65</v>
       </c>
-      <c r="BG297">
-        <v>1.34</v>
-      </c>
-      <c r="BH297">
-        <v>2.9</v>
-      </c>
-      <c r="BI297">
-        <v>1.58</v>
-      </c>
-      <c r="BJ297">
-        <v>2.2</v>
-      </c>
-      <c r="BK297">
-        <v>1.95</v>
-      </c>
-      <c r="BL297">
-        <v>1.75</v>
-      </c>
-      <c r="BM297">
-        <v>2.43</v>
-      </c>
-      <c r="BN297">
-        <v>1.47</v>
-      </c>
-      <c r="BO297">
-        <v>3.15</v>
-      </c>
       <c r="BP297">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="298" spans="1:68">
@@ -62792,7 +62792,7 @@
         <v>297</v>
       </c>
       <c r="B298">
-        <v>7727171</v>
+        <v>7727170</v>
       </c>
       <c r="C298" t="s">
         <v>68</v>
@@ -62807,190 +62807,190 @@
         <v>27</v>
       </c>
       <c r="G298" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H298" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I298">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K298">
+        <v>2</v>
+      </c>
+      <c r="L298">
+        <v>1</v>
+      </c>
+      <c r="M298">
+        <v>3</v>
+      </c>
+      <c r="N298">
         <v>4</v>
       </c>
-      <c r="L298">
-        <v>4</v>
-      </c>
-      <c r="M298">
-        <v>2</v>
-      </c>
-      <c r="N298">
-        <v>6</v>
-      </c>
       <c r="O298" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="P298" t="s">
         <v>405</v>
       </c>
       <c r="Q298">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R298">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S298">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="T298">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U298">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V298">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="W298">
+        <v>1.44</v>
+      </c>
+      <c r="X298">
+        <v>7</v>
+      </c>
+      <c r="Y298">
+        <v>1.1</v>
+      </c>
+      <c r="Z298">
+        <v>3.06</v>
+      </c>
+      <c r="AA298">
+        <v>3.19</v>
+      </c>
+      <c r="AB298">
+        <v>1.99</v>
+      </c>
+      <c r="AC298">
+        <v>1.05</v>
+      </c>
+      <c r="AD298">
+        <v>9.5</v>
+      </c>
+      <c r="AE298">
+        <v>1.25</v>
+      </c>
+      <c r="AF298">
+        <v>3.8</v>
+      </c>
+      <c r="AG298">
+        <v>1.85</v>
+      </c>
+      <c r="AH298">
+        <v>1.85</v>
+      </c>
+      <c r="AI298">
+        <v>1.62</v>
+      </c>
+      <c r="AJ298">
+        <v>2.2</v>
+      </c>
+      <c r="AK298">
+        <v>1.7</v>
+      </c>
+      <c r="AL298">
+        <v>1.25</v>
+      </c>
+      <c r="AM298">
         <v>1.3</v>
       </c>
-      <c r="X298">
-        <v>10</v>
-      </c>
-      <c r="Y298">
-        <v>1.06</v>
-      </c>
-      <c r="Z298">
-        <v>2.31</v>
-      </c>
-      <c r="AA298">
-        <v>2.91</v>
-      </c>
-      <c r="AB298">
-        <v>2.74</v>
-      </c>
-      <c r="AC298">
-        <v>1.08</v>
-      </c>
-      <c r="AD298">
-        <v>7.5</v>
-      </c>
-      <c r="AE298">
-        <v>1.42</v>
-      </c>
-      <c r="AF298">
-        <v>2.8</v>
-      </c>
-      <c r="AG298">
-        <v>2.12</v>
-      </c>
-      <c r="AH298">
-        <v>1.64</v>
-      </c>
-      <c r="AI298">
-        <v>1.95</v>
-      </c>
-      <c r="AJ298">
-        <v>1.8</v>
-      </c>
-      <c r="AK298">
-        <v>1.4</v>
-      </c>
-      <c r="AL298">
-        <v>1.3</v>
-      </c>
-      <c r="AM298">
-        <v>1.5</v>
-      </c>
       <c r="AN298">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AO298">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AP298">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AQ298">
         <v>1.31</v>
       </c>
       <c r="AR298">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AS298">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AT298">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="AU298">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV298">
+        <v>12</v>
+      </c>
+      <c r="AW298">
         <v>6</v>
-      </c>
-      <c r="AW298">
-        <v>14</v>
       </c>
       <c r="AX298">
         <v>5</v>
       </c>
       <c r="AY298">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AZ298">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BA298">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC298">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD298">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="BE298">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF298">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="BG298">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BH298">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI298">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BJ298">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BK298">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BL298">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="BM298">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="BN298">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO298">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BP298">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="299" spans="1:68">
@@ -62998,7 +62998,7 @@
         <v>298</v>
       </c>
       <c r="B299">
-        <v>7727170</v>
+        <v>7727165</v>
       </c>
       <c r="C299" t="s">
         <v>68</v>
@@ -63013,49 +63013,49 @@
         <v>27</v>
       </c>
       <c r="G299" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H299" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J299">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K299">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L299">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M299">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N299">
         <v>4</v>
       </c>
       <c r="O299" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="P299" t="s">
-        <v>406</v>
+        <v>152</v>
       </c>
       <c r="Q299">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R299">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S299">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="T299">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U299">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V299">
         <v>2.63</v>
@@ -63064,19 +63064,19 @@
         <v>1.44</v>
       </c>
       <c r="X299">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y299">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z299">
-        <v>3.06</v>
+        <v>3.52</v>
       </c>
       <c r="AA299">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="AB299">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AC299">
         <v>1.05</v>
@@ -63088,52 +63088,52 @@
         <v>1.25</v>
       </c>
       <c r="AF299">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AG299">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH299">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AI299">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ299">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK299">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AL299">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM299">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN299">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="AO299">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="AP299">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AQ299">
-        <v>1.31</v>
+        <v>1.92</v>
       </c>
       <c r="AR299">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AS299">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AT299">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AU299">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV299">
         <v>12</v>
@@ -63142,61 +63142,61 @@
         <v>6</v>
       </c>
       <c r="AX299">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AY299">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ299">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BA299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB299">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="BC299">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="BD299">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="BE299">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BF299">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="BG299">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BH299">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI299">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="BJ299">
-        <v>2.43</v>
+        <v>3.05</v>
       </c>
       <c r="BK299">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="BL299">
-        <v>1.92</v>
+        <v>2.33</v>
       </c>
       <c r="BM299">
-        <v>2.23</v>
+        <v>1.82</v>
       </c>
       <c r="BN299">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="BO299">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="BP299">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="300" spans="1:68">
@@ -63204,7 +63204,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>7727165</v>
+        <v>7727164</v>
       </c>
       <c r="C300" t="s">
         <v>68</v>
@@ -63219,25 +63219,25 @@
         <v>27</v>
       </c>
       <c r="G300" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H300" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I300">
         <v>1</v>
       </c>
       <c r="J300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K300">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N300">
         <v>4</v>
@@ -63246,16 +63246,16 @@
         <v>279</v>
       </c>
       <c r="P300" t="s">
-        <v>152</v>
+        <v>406</v>
       </c>
       <c r="Q300">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R300">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S300">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="T300">
         <v>1.33</v>
@@ -63276,133 +63276,133 @@
         <v>1.11</v>
       </c>
       <c r="Z300">
-        <v>3.52</v>
+        <v>1.42</v>
       </c>
       <c r="AA300">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="AB300">
-        <v>1.82</v>
+        <v>5.5</v>
       </c>
       <c r="AC300">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD300">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AE300">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF300">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AG300">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH300">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AI300">
+        <v>1.8</v>
+      </c>
+      <c r="AJ300">
+        <v>1.95</v>
+      </c>
+      <c r="AK300">
+        <v>1.12</v>
+      </c>
+      <c r="AL300">
+        <v>1.17</v>
+      </c>
+      <c r="AM300">
+        <v>2.55</v>
+      </c>
+      <c r="AN300">
         <v>1.67</v>
       </c>
-      <c r="AJ300">
-        <v>2.1</v>
-      </c>
-      <c r="AK300">
-        <v>1.93</v>
-      </c>
-      <c r="AL300">
-        <v>1.22</v>
-      </c>
-      <c r="AM300">
-        <v>1.22</v>
-      </c>
-      <c r="AN300">
-        <v>1.36</v>
-      </c>
       <c r="AO300">
-        <v>2.08</v>
+        <v>0.42</v>
       </c>
       <c r="AP300">
         <v>1.5</v>
       </c>
       <c r="AQ300">
-        <v>1.92</v>
+        <v>0.46</v>
       </c>
       <c r="AR300">
-        <v>1.08</v>
+        <v>1.64</v>
       </c>
       <c r="AS300">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AT300">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="AU300">
         <v>6</v>
       </c>
       <c r="AV300">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AW300">
+        <v>13</v>
+      </c>
+      <c r="AX300">
+        <v>3</v>
+      </c>
+      <c r="AY300">
+        <v>19</v>
+      </c>
+      <c r="AZ300">
         <v>6</v>
       </c>
-      <c r="AX300">
-        <v>17</v>
-      </c>
-      <c r="AY300">
-        <v>12</v>
-      </c>
-      <c r="AZ300">
-        <v>36</v>
-      </c>
       <c r="BA300">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BB300">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BC300">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BD300">
+        <v>1.35</v>
+      </c>
+      <c r="BE300">
+        <v>7.5</v>
+      </c>
+      <c r="BF300">
+        <v>3.45</v>
+      </c>
+      <c r="BG300">
+        <v>1.24</v>
+      </c>
+      <c r="BH300">
+        <v>3.55</v>
+      </c>
+      <c r="BI300">
+        <v>1.41</v>
+      </c>
+      <c r="BJ300">
+        <v>2.65</v>
+      </c>
+      <c r="BK300">
+        <v>1.67</v>
+      </c>
+      <c r="BL300">
+        <v>2.05</v>
+      </c>
+      <c r="BM300">
+        <v>2.05</v>
+      </c>
+      <c r="BN300">
+        <v>1.67</v>
+      </c>
+      <c r="BO300">
         <v>2.55</v>
       </c>
-      <c r="BE300">
-        <v>7</v>
-      </c>
-      <c r="BF300">
-        <v>1.6</v>
-      </c>
-      <c r="BG300">
-        <v>1.18</v>
-      </c>
-      <c r="BH300">
-        <v>4.1</v>
-      </c>
-      <c r="BI300">
-        <v>1.3</v>
-      </c>
-      <c r="BJ300">
-        <v>3.05</v>
-      </c>
-      <c r="BK300">
-        <v>1.52</v>
-      </c>
-      <c r="BL300">
-        <v>2.33</v>
-      </c>
-      <c r="BM300">
-        <v>1.82</v>
-      </c>
-      <c r="BN300">
-        <v>1.86</v>
-      </c>
-      <c r="BO300">
-        <v>2.25</v>
-      </c>
       <c r="BP300">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="301" spans="1:68">
@@ -64227,6 +64227,212 @@
       </c>
       <c r="BP304">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7727184</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45680.70833333334</v>
+      </c>
+      <c r="F305">
+        <v>28</v>
+      </c>
+      <c r="G305" t="s">
+        <v>71</v>
+      </c>
+      <c r="H305" t="s">
+        <v>80</v>
+      </c>
+      <c r="I305">
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <v>1</v>
+      </c>
+      <c r="K305">
+        <v>2</v>
+      </c>
+      <c r="L305">
+        <v>1</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>2</v>
+      </c>
+      <c r="O305" t="s">
+        <v>254</v>
+      </c>
+      <c r="P305" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q305">
+        <v>4</v>
+      </c>
+      <c r="R305">
+        <v>2.05</v>
+      </c>
+      <c r="S305">
+        <v>2.88</v>
+      </c>
+      <c r="T305">
+        <v>1.44</v>
+      </c>
+      <c r="U305">
+        <v>2.63</v>
+      </c>
+      <c r="V305">
+        <v>3.25</v>
+      </c>
+      <c r="W305">
+        <v>1.33</v>
+      </c>
+      <c r="X305">
+        <v>10</v>
+      </c>
+      <c r="Y305">
+        <v>1.06</v>
+      </c>
+      <c r="Z305">
+        <v>3.2</v>
+      </c>
+      <c r="AA305">
+        <v>3.2</v>
+      </c>
+      <c r="AB305">
+        <v>2.15</v>
+      </c>
+      <c r="AC305">
+        <v>1.06</v>
+      </c>
+      <c r="AD305">
+        <v>10</v>
+      </c>
+      <c r="AE305">
+        <v>1.36</v>
+      </c>
+      <c r="AF305">
+        <v>3.1</v>
+      </c>
+      <c r="AG305">
+        <v>2.1</v>
+      </c>
+      <c r="AH305">
+        <v>1.67</v>
+      </c>
+      <c r="AI305">
+        <v>1.91</v>
+      </c>
+      <c r="AJ305">
+        <v>1.91</v>
+      </c>
+      <c r="AK305">
+        <v>1.7</v>
+      </c>
+      <c r="AL305">
+        <v>1.25</v>
+      </c>
+      <c r="AM305">
+        <v>1.33</v>
+      </c>
+      <c r="AN305">
+        <v>2.71</v>
+      </c>
+      <c r="AO305">
+        <v>2.17</v>
+      </c>
+      <c r="AP305">
+        <v>2.6</v>
+      </c>
+      <c r="AQ305">
+        <v>2.08</v>
+      </c>
+      <c r="AR305">
+        <v>1.4</v>
+      </c>
+      <c r="AS305">
+        <v>1.17</v>
+      </c>
+      <c r="AT305">
+        <v>2.57</v>
+      </c>
+      <c r="AU305">
+        <v>8</v>
+      </c>
+      <c r="AV305">
+        <v>2</v>
+      </c>
+      <c r="AW305">
+        <v>6</v>
+      </c>
+      <c r="AX305">
+        <v>6</v>
+      </c>
+      <c r="AY305">
+        <v>18</v>
+      </c>
+      <c r="AZ305">
+        <v>12</v>
+      </c>
+      <c r="BA305">
+        <v>5</v>
+      </c>
+      <c r="BB305">
+        <v>5</v>
+      </c>
+      <c r="BC305">
+        <v>10</v>
+      </c>
+      <c r="BD305">
+        <v>2.51</v>
+      </c>
+      <c r="BE305">
+        <v>6.6</v>
+      </c>
+      <c r="BF305">
+        <v>1.84</v>
+      </c>
+      <c r="BG305">
+        <v>1.2</v>
+      </c>
+      <c r="BH305">
+        <v>3.72</v>
+      </c>
+      <c r="BI305">
+        <v>1.41</v>
+      </c>
+      <c r="BJ305">
+        <v>2.6</v>
+      </c>
+      <c r="BK305">
+        <v>1.73</v>
+      </c>
+      <c r="BL305">
+        <v>1.99</v>
+      </c>
+      <c r="BM305">
+        <v>2.17</v>
+      </c>
+      <c r="BN305">
+        <v>1.58</v>
+      </c>
+      <c r="BO305">
+        <v>2.88</v>
+      </c>
+      <c r="BP305">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
